--- a/lcoe_plots/sc_esc_ethylene_lcoe/LCOE_SC_ESC_Ethylene.xlsx
+++ b/lcoe_plots/sc_esc_ethylene_lcoe/LCOE_SC_ESC_Ethylene.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/MacroEnergy-Abbie.jl/MacroEnergyExamples/lcoe_plots/sc_esc_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3A8EAA-04ED-7847-B3C5-DD93FA98CC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038EE2F2-C078-214B-8BA3-18871465BFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
+    <sheet name="lc_summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="148">
   <si>
     <t>Asset Parameters (normalized by commodity feedstock)</t>
   </si>
@@ -457,6 +458,27 @@
   <si>
     <t>Diff. Between Input and Output CO2 (t-CO2/t-ethylene)</t>
   </si>
+  <si>
+    <t>LCOE ($/GJ-ethylene)</t>
+  </si>
+  <si>
+    <t>CHECK LCOE ($/GJ-ethylene)</t>
+  </si>
+  <si>
+    <t>LCOE for steam/electric cracker ($/GJ-ethylene) - CHEMICALS SEQUESTRATION</t>
+  </si>
+  <si>
+    <t>LCOE for steam/electric cracker ($/GJ-ethylene) - NO CHEMICALS SEQUESTRATION</t>
+  </si>
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Ethylene LHV</t>
+  </si>
+  <si>
+    <t>GJ/t-ethylene</t>
+  </si>
 </sst>
 </file>
 
@@ -465,7 +487,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -497,6 +519,22 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -600,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -619,6 +657,12 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1596,7 +1640,7 @@
         <v>1.6761597559999999</v>
       </c>
       <c r="O5" s="11">
-        <f t="shared" ref="O4:O35" si="36">CC5/0.22/14</f>
+        <f t="shared" ref="O5:O35" si="36">CC5/0.22/14</f>
         <v>0.19808570333027159</v>
       </c>
       <c r="Q5" s="16">
@@ -1798,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="CC5" s="10">
-        <f t="shared" ref="CC4:CC35" si="38">BW5-SUM(BY5:CB5)</f>
+        <f t="shared" ref="CC5:CC35" si="38">BW5-SUM(BY5:CB5)</f>
         <v>0.61010396625723651</v>
       </c>
       <c r="CD5" s="10">
@@ -17816,4 +17860,8893 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109F3854-62D5-624F-987E-C6BD8DAE78EF}">
+  <dimension ref="B2:AN66"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5" customWidth="1"/>
+    <col min="19" max="19" width="2.83203125" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="22" max="22" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.1640625" customWidth="1"/>
+    <col min="38" max="38" width="11.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:40" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="T2" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AL2" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM2"/>
+      <c r="AN2"/>
+    </row>
+    <row r="3" spans="2:40" ht="48" x14ac:dyDescent="0.2">
+      <c r="B3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="R3" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI3" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ3" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM3">
+        <v>45.6</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B4" t="str">
+        <f>lc_detailed!AM4</f>
+        <v>CA_TSC</v>
+      </c>
+      <c r="C4" t="str">
+        <f>lc_detailed!AN4</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D4" s="21">
+        <f>lc_detailed!AU4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="21">
+        <f>lc_detailed!AV4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="21">
+        <f>lc_detailed!AW4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="21">
+        <f>lc_detailed!AX4/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H4" s="21">
+        <f>lc_detailed!AY4/$AM$3</f>
+        <v>-2.9399663335483529E-2</v>
+      </c>
+      <c r="I4" s="21">
+        <f>lc_detailed!AZ4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="21">
+        <f>lc_detailed!BA4/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K4" s="21">
+        <f>lc_detailed!BB4/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L4" s="21">
+        <f>lc_detailed!BC4/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M4" s="21">
+        <f>lc_detailed!BE4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="21">
+        <f>lc_detailed!BF4/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O4" s="21">
+        <f>lc_detailed!BD4</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P4" s="21">
+        <f>lc_detailed!AO4</f>
+        <v>861.01391931183161</v>
+      </c>
+      <c r="Q4" s="21">
+        <f>P4/$AM$3</f>
+        <v>18.881884195434903</v>
+      </c>
+      <c r="R4" s="21">
+        <f>SUM(D4:N4)</f>
+        <v>18.881884195434903</v>
+      </c>
+      <c r="T4" t="str">
+        <f>lc_detailed!AM4</f>
+        <v>CA_TSC</v>
+      </c>
+      <c r="U4" t="str">
+        <f>lc_detailed!AN4</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V4" s="21">
+        <f>lc_detailed!AU4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="21">
+        <f>lc_detailed!AV4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X4" s="21">
+        <f>lc_detailed!AW4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="21">
+        <f>lc_detailed!AX4/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z4" s="21">
+        <f>lc_detailed!AY4/$AM$3</f>
+        <v>-2.9399663335483529E-2</v>
+      </c>
+      <c r="AA4" s="21">
+        <f>lc_detailed!AZ4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="21">
+        <f>lc_detailed!BA4/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC4" s="21">
+        <f>lc_detailed!BB4/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD4" s="21">
+        <f>lc_detailed!BC4/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE4" s="21">
+        <f>lc_detailed!BK4/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="21">
+        <f>lc_detailed!BL4/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG4" s="21">
+        <f>lc_detailed!BJ4</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH4" s="21">
+        <f>lc_detailed!AR4</f>
+        <v>1235.6991744234729</v>
+      </c>
+      <c r="AI4" s="21">
+        <f>AH4/$AM$3</f>
+        <v>27.098666105777912</v>
+      </c>
+      <c r="AJ4" s="21">
+        <f>SUM(V4:AF4)</f>
+        <v>27.098666105777912</v>
+      </c>
+    </row>
+    <row r="5" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B5" t="str">
+        <f>lc_detailed!AM5</f>
+        <v>SW_TSC</v>
+      </c>
+      <c r="C5" t="str">
+        <f>lc_detailed!AN5</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D5" s="21">
+        <f>lc_detailed!AU5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="21">
+        <f>lc_detailed!AV5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <f>lc_detailed!AW5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="21">
+        <f>lc_detailed!AX5/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H5" s="21">
+        <f>lc_detailed!AY5/$AM$3</f>
+        <v>-1.1980339652309062E-2</v>
+      </c>
+      <c r="I5" s="21">
+        <f>lc_detailed!AZ5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="21">
+        <f>lc_detailed!BA5/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K5" s="21">
+        <f>lc_detailed!BB5/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L5" s="21">
+        <f>lc_detailed!BC5/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M5" s="21">
+        <f>lc_detailed!BE5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="21">
+        <f>lc_detailed!BF5/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O5" s="21">
+        <f>lc_detailed!BD5</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P5" s="21">
+        <f>lc_detailed!AO5</f>
+        <v>861.8082404717843</v>
+      </c>
+      <c r="Q5" s="21">
+        <f t="shared" ref="Q5:Q66" si="0">P5/$AM$3</f>
+        <v>18.899303519118074</v>
+      </c>
+      <c r="R5" s="21">
+        <f t="shared" ref="R5:R66" si="1">SUM(D5:N5)</f>
+        <v>18.899303519118078</v>
+      </c>
+      <c r="T5" t="str">
+        <f>lc_detailed!AM5</f>
+        <v>SW_TSC</v>
+      </c>
+      <c r="U5" t="str">
+        <f>lc_detailed!AN5</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V5" s="21">
+        <f>lc_detailed!AU5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="21">
+        <f>lc_detailed!AV5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="21">
+        <f>lc_detailed!AW5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="21">
+        <f>lc_detailed!AX5/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z5" s="21">
+        <f>lc_detailed!AY5/$AM$3</f>
+        <v>-1.1980339652309062E-2</v>
+      </c>
+      <c r="AA5" s="21">
+        <f>lc_detailed!AZ5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="21">
+        <f>lc_detailed!BA5/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC5" s="21">
+        <f>lc_detailed!BB5/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD5" s="21">
+        <f>lc_detailed!BC5/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE5" s="21">
+        <f>lc_detailed!BK5/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="21">
+        <f>lc_detailed!BL5/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG5" s="21">
+        <f>lc_detailed!BJ5</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH5" s="21">
+        <f>lc_detailed!AR5</f>
+        <v>1236.4934955834256</v>
+      </c>
+      <c r="AI5" s="21">
+        <f t="shared" ref="AI5:AI66" si="2">AH5/$AM$3</f>
+        <v>27.116085429461087</v>
+      </c>
+      <c r="AJ5" s="21">
+        <f t="shared" ref="AJ5:AJ66" si="3">SUM(V5:AF5)</f>
+        <v>27.116085429461087</v>
+      </c>
+    </row>
+    <row r="6" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B6" t="str">
+        <f>lc_detailed!AM6</f>
+        <v>NW_TSC</v>
+      </c>
+      <c r="C6" t="str">
+        <f>lc_detailed!AN6</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D6" s="21">
+        <f>lc_detailed!AU6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="21">
+        <f>lc_detailed!AV6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <f>lc_detailed!AW6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="21">
+        <f>lc_detailed!AX6/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H6" s="21">
+        <f>lc_detailed!AY6/$AM$3</f>
+        <v>-2.2863492234672874E-2</v>
+      </c>
+      <c r="I6" s="21">
+        <f>lc_detailed!AZ6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="21">
+        <f>lc_detailed!BA6/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K6" s="21">
+        <f>lc_detailed!BB6/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L6" s="21">
+        <f>lc_detailed!BC6/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M6" s="21">
+        <f>lc_detailed!BE6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="21">
+        <f>lc_detailed!BF6/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O6" s="21">
+        <f>lc_detailed!BD6</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P6" s="21">
+        <f>lc_detailed!AO6</f>
+        <v>861.31196871402858</v>
+      </c>
+      <c r="Q6" s="21">
+        <f t="shared" si="0"/>
+        <v>18.888420366535716</v>
+      </c>
+      <c r="R6" s="21">
+        <f t="shared" si="1"/>
+        <v>18.888420366535712</v>
+      </c>
+      <c r="T6" t="str">
+        <f>lc_detailed!AM6</f>
+        <v>NW_TSC</v>
+      </c>
+      <c r="U6" t="str">
+        <f>lc_detailed!AN6</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V6" s="21">
+        <f>lc_detailed!AU6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="21">
+        <f>lc_detailed!AV6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="21">
+        <f>lc_detailed!AW6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="21">
+        <f>lc_detailed!AX6/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z6" s="21">
+        <f>lc_detailed!AY6/$AM$3</f>
+        <v>-2.2863492234672874E-2</v>
+      </c>
+      <c r="AA6" s="21">
+        <f>lc_detailed!AZ6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="21">
+        <f>lc_detailed!BA6/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC6" s="21">
+        <f>lc_detailed!BB6/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD6" s="21">
+        <f>lc_detailed!BC6/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE6" s="21">
+        <f>lc_detailed!BK6/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="21">
+        <f>lc_detailed!BL6/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG6" s="21">
+        <f>lc_detailed!BJ6</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH6" s="21">
+        <f>lc_detailed!AR6</f>
+        <v>1235.9972238256698</v>
+      </c>
+      <c r="AI6" s="21">
+        <f t="shared" si="2"/>
+        <v>27.105202276878725</v>
+      </c>
+      <c r="AJ6" s="21">
+        <f t="shared" si="3"/>
+        <v>27.105202276878721</v>
+      </c>
+    </row>
+    <row r="7" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B7" t="str">
+        <f>lc_detailed!AM7</f>
+        <v>TX_TSC</v>
+      </c>
+      <c r="C7" t="str">
+        <f>lc_detailed!AN7</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D7" s="21">
+        <f>lc_detailed!AU7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="21">
+        <f>lc_detailed!AV7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <f>lc_detailed!AW7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="21">
+        <f>lc_detailed!AX7/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H7" s="21">
+        <f>lc_detailed!AY7/$AM$3</f>
+        <v>-1.388652757205903E-2</v>
+      </c>
+      <c r="I7" s="21">
+        <f>lc_detailed!AZ7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="21">
+        <f>lc_detailed!BA7/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K7" s="21">
+        <f>lc_detailed!BB7/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L7" s="21">
+        <f>lc_detailed!BC7/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M7" s="21">
+        <f>lc_detailed!BE7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="21">
+        <f>lc_detailed!BF7/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O7" s="21">
+        <f>lc_detailed!BD7</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P7" s="21">
+        <f>lc_detailed!AO7</f>
+        <v>861.72131830264379</v>
+      </c>
+      <c r="Q7" s="21">
+        <f t="shared" si="0"/>
+        <v>18.897397331198327</v>
+      </c>
+      <c r="R7" s="21">
+        <f t="shared" si="1"/>
+        <v>18.897397331198327</v>
+      </c>
+      <c r="T7" t="str">
+        <f>lc_detailed!AM7</f>
+        <v>TX_TSC</v>
+      </c>
+      <c r="U7" t="str">
+        <f>lc_detailed!AN7</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V7" s="21">
+        <f>lc_detailed!AU7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="21">
+        <f>lc_detailed!AV7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="21">
+        <f>lc_detailed!AW7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="21">
+        <f>lc_detailed!AX7/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z7" s="21">
+        <f>lc_detailed!AY7/$AM$3</f>
+        <v>-1.388652757205903E-2</v>
+      </c>
+      <c r="AA7" s="21">
+        <f>lc_detailed!AZ7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="21">
+        <f>lc_detailed!BA7/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC7" s="21">
+        <f>lc_detailed!BB7/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD7" s="21">
+        <f>lc_detailed!BC7/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE7" s="21">
+        <f>lc_detailed!BK7/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="21">
+        <f>lc_detailed!BL7/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG7" s="21">
+        <f>lc_detailed!BJ7</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH7" s="21">
+        <f>lc_detailed!AR7</f>
+        <v>1236.406573414285</v>
+      </c>
+      <c r="AI7" s="21">
+        <f t="shared" si="2"/>
+        <v>27.114179241541336</v>
+      </c>
+      <c r="AJ7" s="21">
+        <f t="shared" si="3"/>
+        <v>27.114179241541336</v>
+      </c>
+    </row>
+    <row r="8" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B8" t="str">
+        <f>lc_detailed!AM8</f>
+        <v>NCEN_TSC</v>
+      </c>
+      <c r="C8" t="str">
+        <f>lc_detailed!AN8</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D8" s="21">
+        <f>lc_detailed!AU8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="21">
+        <f>lc_detailed!AV8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="21">
+        <f>lc_detailed!AW8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="21">
+        <f>lc_detailed!AX8/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H8" s="21">
+        <f>lc_detailed!AY8/$AM$3</f>
+        <v>-7.7325109559540734E-3</v>
+      </c>
+      <c r="I8" s="21">
+        <f>lc_detailed!AZ8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="21">
+        <f>lc_detailed!BA8/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K8" s="21">
+        <f>lc_detailed!BB8/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L8" s="21">
+        <f>lc_detailed!BC8/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M8" s="21">
+        <f>lc_detailed!BE8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="21">
+        <f>lc_detailed!BF8/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O8" s="21">
+        <f>lc_detailed!BD8</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P8" s="21">
+        <f>lc_detailed!AO8</f>
+        <v>862.00194146033823</v>
+      </c>
+      <c r="Q8" s="21">
+        <f t="shared" si="0"/>
+        <v>18.903551347814435</v>
+      </c>
+      <c r="R8" s="21">
+        <f t="shared" si="1"/>
+        <v>18.903551347814432</v>
+      </c>
+      <c r="T8" t="str">
+        <f>lc_detailed!AM8</f>
+        <v>NCEN_TSC</v>
+      </c>
+      <c r="U8" t="str">
+        <f>lc_detailed!AN8</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V8" s="21">
+        <f>lc_detailed!AU8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="21">
+        <f>lc_detailed!AV8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="21">
+        <f>lc_detailed!AW8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="21">
+        <f>lc_detailed!AX8/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z8" s="21">
+        <f>lc_detailed!AY8/$AM$3</f>
+        <v>-7.7325109559540734E-3</v>
+      </c>
+      <c r="AA8" s="21">
+        <f>lc_detailed!AZ8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="21">
+        <f>lc_detailed!BA8/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC8" s="21">
+        <f>lc_detailed!BB8/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD8" s="21">
+        <f>lc_detailed!BC8/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE8" s="21">
+        <f>lc_detailed!BK8/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="21">
+        <f>lc_detailed!BL8/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG8" s="21">
+        <f>lc_detailed!BJ8</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH8" s="21">
+        <f>lc_detailed!AR8</f>
+        <v>1236.6871965719795</v>
+      </c>
+      <c r="AI8" s="21">
+        <f t="shared" si="2"/>
+        <v>27.120333258157444</v>
+      </c>
+      <c r="AJ8" s="21">
+        <f t="shared" si="3"/>
+        <v>27.120333258157441</v>
+      </c>
+    </row>
+    <row r="9" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B9" t="str">
+        <f>lc_detailed!AM9</f>
+        <v>CEN_TSC</v>
+      </c>
+      <c r="C9" t="str">
+        <f>lc_detailed!AN9</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D9" s="21">
+        <f>lc_detailed!AU9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="21">
+        <f>lc_detailed!AV9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
+        <f>lc_detailed!AW9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="21">
+        <f>lc_detailed!AX9/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H9" s="21">
+        <f>lc_detailed!AY9/$AM$3</f>
+        <v>-1.3420286350359913E-2</v>
+      </c>
+      <c r="I9" s="21">
+        <f>lc_detailed!AZ9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="21">
+        <f>lc_detailed!BA9/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K9" s="21">
+        <f>lc_detailed!BB9/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L9" s="21">
+        <f>lc_detailed!BC9/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M9" s="21">
+        <f>lc_detailed!BE9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="21">
+        <f>lc_detailed!BF9/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O9" s="21">
+        <f>lc_detailed!BD9</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P9" s="21">
+        <f>lc_detailed!AO9</f>
+        <v>861.74257890235322</v>
+      </c>
+      <c r="Q9" s="21">
+        <f t="shared" si="0"/>
+        <v>18.897863572420025</v>
+      </c>
+      <c r="R9" s="21">
+        <f t="shared" si="1"/>
+        <v>18.897863572420025</v>
+      </c>
+      <c r="T9" t="str">
+        <f>lc_detailed!AM9</f>
+        <v>CEN_TSC</v>
+      </c>
+      <c r="U9" t="str">
+        <f>lc_detailed!AN9</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V9" s="21">
+        <f>lc_detailed!AU9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="21">
+        <f>lc_detailed!AV9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="21">
+        <f>lc_detailed!AW9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="21">
+        <f>lc_detailed!AX9/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z9" s="21">
+        <f>lc_detailed!AY9/$AM$3</f>
+        <v>-1.3420286350359913E-2</v>
+      </c>
+      <c r="AA9" s="21">
+        <f>lc_detailed!AZ9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="21">
+        <f>lc_detailed!BA9/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC9" s="21">
+        <f>lc_detailed!BB9/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD9" s="21">
+        <f>lc_detailed!BC9/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE9" s="21">
+        <f>lc_detailed!BK9/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="21">
+        <f>lc_detailed!BL9/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG9" s="21">
+        <f>lc_detailed!BJ9</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH9" s="21">
+        <f>lc_detailed!AR9</f>
+        <v>1236.4278340139945</v>
+      </c>
+      <c r="AI9" s="21">
+        <f t="shared" si="2"/>
+        <v>27.114645482763034</v>
+      </c>
+      <c r="AJ9" s="21">
+        <f t="shared" si="3"/>
+        <v>27.114645482763034</v>
+      </c>
+    </row>
+    <row r="10" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B10" t="str">
+        <f>lc_detailed!AM10</f>
+        <v>SE_TSC</v>
+      </c>
+      <c r="C10" t="str">
+        <f>lc_detailed!AN10</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D10" s="21">
+        <f>lc_detailed!AU10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="21">
+        <f>lc_detailed!AV10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <f>lc_detailed!AW10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="21">
+        <f>lc_detailed!AX10/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H10" s="21">
+        <f>lc_detailed!AY10/$AM$3</f>
+        <v>-1.3616107475968278E-2</v>
+      </c>
+      <c r="I10" s="21">
+        <f>lc_detailed!AZ10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="21">
+        <f>lc_detailed!BA10/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K10" s="21">
+        <f>lc_detailed!BB10/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L10" s="21">
+        <f>lc_detailed!BC10/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M10" s="21">
+        <f>lc_detailed!BE10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="21">
+        <f>lc_detailed!BF10/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O10" s="21">
+        <f>lc_detailed!BD10</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P10" s="21">
+        <f>lc_detailed!AO10</f>
+        <v>861.7336494590254</v>
+      </c>
+      <c r="Q10" s="21">
+        <f t="shared" si="0"/>
+        <v>18.897667751294417</v>
+      </c>
+      <c r="R10" s="21">
+        <f t="shared" si="1"/>
+        <v>18.897667751294417</v>
+      </c>
+      <c r="T10" t="str">
+        <f>lc_detailed!AM10</f>
+        <v>SE_TSC</v>
+      </c>
+      <c r="U10" t="str">
+        <f>lc_detailed!AN10</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V10" s="21">
+        <f>lc_detailed!AU10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="21">
+        <f>lc_detailed!AV10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X10" s="21">
+        <f>lc_detailed!AW10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="21">
+        <f>lc_detailed!AX10/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z10" s="21">
+        <f>lc_detailed!AY10/$AM$3</f>
+        <v>-1.3616107475968278E-2</v>
+      </c>
+      <c r="AA10" s="21">
+        <f>lc_detailed!AZ10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="21">
+        <f>lc_detailed!BA10/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC10" s="21">
+        <f>lc_detailed!BB10/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD10" s="21">
+        <f>lc_detailed!BC10/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE10" s="21">
+        <f>lc_detailed!BK10/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="21">
+        <f>lc_detailed!BL10/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG10" s="21">
+        <f>lc_detailed!BJ10</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH10" s="21">
+        <f>lc_detailed!AR10</f>
+        <v>1236.4189045706667</v>
+      </c>
+      <c r="AI10" s="21">
+        <f t="shared" si="2"/>
+        <v>27.114449661637426</v>
+      </c>
+      <c r="AJ10" s="21">
+        <f t="shared" si="3"/>
+        <v>27.114449661637426</v>
+      </c>
+    </row>
+    <row r="11" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B11" t="str">
+        <f>lc_detailed!AM11</f>
+        <v>MIDAT_TSC</v>
+      </c>
+      <c r="C11" t="str">
+        <f>lc_detailed!AN11</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D11" s="21">
+        <f>lc_detailed!AU11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
+        <f>lc_detailed!AV11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <f>lc_detailed!AW11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="21">
+        <f>lc_detailed!AX11/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H11" s="21">
+        <f>lc_detailed!AY11/$AM$3</f>
+        <v>-8.7210762247168436E-3</v>
+      </c>
+      <c r="I11" s="21">
+        <f>lc_detailed!AZ11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="21">
+        <f>lc_detailed!BA11/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K11" s="21">
+        <f>lc_detailed!BB11/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L11" s="21">
+        <f>lc_detailed!BC11/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M11" s="21">
+        <f>lc_detailed!BE11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="21">
+        <f>lc_detailed!BF11/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O11" s="21">
+        <f>lc_detailed!BD11</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P11" s="21">
+        <f>lc_detailed!AO11</f>
+        <v>861.95686288408251</v>
+      </c>
+      <c r="Q11" s="21">
+        <f t="shared" si="0"/>
+        <v>18.902562782545669</v>
+      </c>
+      <c r="R11" s="21">
+        <f t="shared" si="1"/>
+        <v>18.902562782545669</v>
+      </c>
+      <c r="T11" t="str">
+        <f>lc_detailed!AM11</f>
+        <v>MIDAT_TSC</v>
+      </c>
+      <c r="U11" t="str">
+        <f>lc_detailed!AN11</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V11" s="21">
+        <f>lc_detailed!AU11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="21">
+        <f>lc_detailed!AV11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="21">
+        <f>lc_detailed!AW11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="21">
+        <f>lc_detailed!AX11/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z11" s="21">
+        <f>lc_detailed!AY11/$AM$3</f>
+        <v>-8.7210762247168436E-3</v>
+      </c>
+      <c r="AA11" s="21">
+        <f>lc_detailed!AZ11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="21">
+        <f>lc_detailed!BA11/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC11" s="21">
+        <f>lc_detailed!BB11/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD11" s="21">
+        <f>lc_detailed!BC11/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE11" s="21">
+        <f>lc_detailed!BK11/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="21">
+        <f>lc_detailed!BL11/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG11" s="21">
+        <f>lc_detailed!BJ11</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH11" s="21">
+        <f>lc_detailed!AR11</f>
+        <v>1236.6421179957238</v>
+      </c>
+      <c r="AI11" s="21">
+        <f t="shared" si="2"/>
+        <v>27.119344692888678</v>
+      </c>
+      <c r="AJ11" s="21">
+        <f t="shared" si="3"/>
+        <v>27.119344692888678</v>
+      </c>
+    </row>
+    <row r="12" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B12" t="str">
+        <f>lc_detailed!AM12</f>
+        <v>NE_TSC</v>
+      </c>
+      <c r="C12" t="str">
+        <f>lc_detailed!AN12</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D12" s="21">
+        <f>lc_detailed!AU12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="21">
+        <f>lc_detailed!AV12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="21">
+        <f>lc_detailed!AW12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="21">
+        <f>lc_detailed!AX12/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H12" s="21">
+        <f>lc_detailed!AY12/$AM$3</f>
+        <v>5.5208385176549898E-2</v>
+      </c>
+      <c r="I12" s="21">
+        <f>lc_detailed!AZ12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="21">
+        <f>lc_detailed!BA12/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K12" s="21">
+        <f>lc_detailed!BB12/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L12" s="21">
+        <f>lc_detailed!BC12/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M12" s="21">
+        <f>lc_detailed!BE12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="21">
+        <f>lc_detailed!BF12/$AM$3</f>
+        <v>1.1051347857539076</v>
+      </c>
+      <c r="O12" s="21">
+        <f>lc_detailed!BD12</f>
+        <v>0.50437876878389287</v>
+      </c>
+      <c r="P12" s="21">
+        <f>lc_detailed!AO12</f>
+        <v>864.87204632398038</v>
+      </c>
+      <c r="Q12" s="21">
+        <f t="shared" si="0"/>
+        <v>18.966492243946938</v>
+      </c>
+      <c r="R12" s="21">
+        <f t="shared" si="1"/>
+        <v>18.966492243946938</v>
+      </c>
+      <c r="T12" t="str">
+        <f>lc_detailed!AM12</f>
+        <v>NE_TSC</v>
+      </c>
+      <c r="U12" t="str">
+        <f>lc_detailed!AN12</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V12" s="21">
+        <f>lc_detailed!AU12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="21">
+        <f>lc_detailed!AV12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X12" s="21">
+        <f>lc_detailed!AW12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="21">
+        <f>lc_detailed!AX12/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z12" s="21">
+        <f>lc_detailed!AY12/$AM$3</f>
+        <v>5.5208385176549898E-2</v>
+      </c>
+      <c r="AA12" s="21">
+        <f>lc_detailed!AZ12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="21">
+        <f>lc_detailed!BA12/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC12" s="21">
+        <f>lc_detailed!BB12/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD12" s="21">
+        <f>lc_detailed!BC12/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE12" s="21">
+        <f>lc_detailed!BK12/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="21">
+        <f>lc_detailed!BL12/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG12" s="21">
+        <f>lc_detailed!BJ12</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH12" s="21">
+        <f>lc_detailed!AR12</f>
+        <v>1239.5573014356216</v>
+      </c>
+      <c r="AI12" s="21">
+        <f t="shared" si="2"/>
+        <v>27.183274154289947</v>
+      </c>
+      <c r="AJ12" s="21">
+        <f t="shared" si="3"/>
+        <v>27.183274154289947</v>
+      </c>
+    </row>
+    <row r="13" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B13" t="str">
+        <f>lc_detailed!AM13</f>
+        <v>CA_TSC+CC90</v>
+      </c>
+      <c r="C13" t="str">
+        <f>lc_detailed!AN13</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D13" s="21">
+        <f>lc_detailed!AU13/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="21">
+        <f>lc_detailed!AV13/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="21">
+        <f>lc_detailed!AW13/$AM$3</f>
+        <v>6.3919178273421681E-2</v>
+      </c>
+      <c r="G13" s="21">
+        <f>lc_detailed!AX13/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H13" s="21">
+        <f>lc_detailed!AY13/$AM$3</f>
+        <v>-2.9399663335483529E-2</v>
+      </c>
+      <c r="I13" s="21">
+        <f>lc_detailed!AZ13/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="21">
+        <f>lc_detailed!BA13/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K13" s="21">
+        <f>lc_detailed!BB13/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L13" s="21">
+        <f>lc_detailed!BC13/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M13" s="21">
+        <f>lc_detailed!BE13/$AM$3</f>
+        <v>-0.94098738465269205</v>
+      </c>
+      <c r="N13" s="21">
+        <f>lc_detailed!BF13/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O13" s="21">
+        <f>lc_detailed!BD13</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P13" s="21">
+        <f>lc_detailed!AO13</f>
+        <v>852.13959832307125</v>
+      </c>
+      <c r="Q13" s="21">
+        <f t="shared" si="0"/>
+        <v>18.687271893049807</v>
+      </c>
+      <c r="R13" s="21">
+        <f t="shared" si="1"/>
+        <v>18.687271893049804</v>
+      </c>
+      <c r="T13" t="str">
+        <f>lc_detailed!AM13</f>
+        <v>CA_TSC+CC90</v>
+      </c>
+      <c r="U13" t="str">
+        <f>lc_detailed!AN13</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V13" s="21">
+        <f>lc_detailed!AU13/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="21">
+        <f>lc_detailed!AV13/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="21">
+        <f>lc_detailed!AW13/$AM$3</f>
+        <v>6.3919178273421681E-2</v>
+      </c>
+      <c r="Y13" s="21">
+        <f>lc_detailed!AX13/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z13" s="21">
+        <f>lc_detailed!AY13/$AM$3</f>
+        <v>-2.9399663335483529E-2</v>
+      </c>
+      <c r="AA13" s="21">
+        <f>lc_detailed!AZ13/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="21">
+        <f>lc_detailed!BA13/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC13" s="21">
+        <f>lc_detailed!BB13/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD13" s="21">
+        <f>lc_detailed!BC13/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE13" s="21">
+        <f>lc_detailed!BK13/$AM$3</f>
+        <v>-0.94098738465269205</v>
+      </c>
+      <c r="AF13" s="21">
+        <f>lc_detailed!BL13/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG13" s="21">
+        <f>lc_detailed!BJ13</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH13" s="21">
+        <f>lc_detailed!AR13</f>
+        <v>1226.8248534253048</v>
+      </c>
+      <c r="AI13" s="21">
+        <f t="shared" si="2"/>
+        <v>26.904053803186507</v>
+      </c>
+      <c r="AJ13" s="21">
+        <f t="shared" si="3"/>
+        <v>26.904053803186503</v>
+      </c>
+    </row>
+    <row r="14" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B14" t="str">
+        <f>lc_detailed!AM14</f>
+        <v>CA_TSC:H2</v>
+      </c>
+      <c r="C14" t="str">
+        <f>lc_detailed!AN14</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D14" s="21">
+        <f>lc_detailed!AU14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="21">
+        <f>lc_detailed!AV14/$AM$3</f>
+        <v>-0.30639510581400747</v>
+      </c>
+      <c r="F14" s="21">
+        <f>lc_detailed!AW14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="21">
+        <f>lc_detailed!AX14/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H14" s="21">
+        <f>lc_detailed!AY14/$AM$3</f>
+        <v>-0.17072840509347034</v>
+      </c>
+      <c r="I14" s="21">
+        <f>lc_detailed!AZ14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="21">
+        <f>lc_detailed!BA14/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K14" s="21">
+        <f>lc_detailed!BB14/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L14" s="21">
+        <f>lc_detailed!BC14/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M14" s="21">
+        <f>lc_detailed!BE14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="21">
+        <f>lc_detailed!BF14/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O14" s="21">
+        <f>lc_detailed!BD14</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P14" s="21">
+        <f>lc_detailed!AO14</f>
+        <v>877.77297538597509</v>
+      </c>
+      <c r="Q14" s="21">
+        <f t="shared" si="0"/>
+        <v>19.249407354955594</v>
+      </c>
+      <c r="R14" s="21">
+        <f t="shared" si="1"/>
+        <v>19.249407354955594</v>
+      </c>
+      <c r="T14" t="str">
+        <f>lc_detailed!AM14</f>
+        <v>CA_TSC:H2</v>
+      </c>
+      <c r="U14" t="str">
+        <f>lc_detailed!AN14</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V14" s="21">
+        <f>lc_detailed!AU14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="21">
+        <f>lc_detailed!AV14/$AM$3</f>
+        <v>-0.30639510581400747</v>
+      </c>
+      <c r="X14" s="21">
+        <f>lc_detailed!AW14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="21">
+        <f>lc_detailed!AX14/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z14" s="21">
+        <f>lc_detailed!AY14/$AM$3</f>
+        <v>-0.17072840509347034</v>
+      </c>
+      <c r="AA14" s="21">
+        <f>lc_detailed!AZ14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="21">
+        <f>lc_detailed!BA14/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC14" s="21">
+        <f>lc_detailed!BB14/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD14" s="21">
+        <f>lc_detailed!BC14/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE14" s="21">
+        <f>lc_detailed!BK14/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="21">
+        <f>lc_detailed!BL14/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG14" s="21">
+        <f>lc_detailed!BJ14</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH14" s="21">
+        <f>lc_detailed!AR14</f>
+        <v>1252.4582305011229</v>
+      </c>
+      <c r="AI14" s="21">
+        <f t="shared" si="2"/>
+        <v>27.466189265375501</v>
+      </c>
+      <c r="AJ14" s="21">
+        <f t="shared" si="3"/>
+        <v>27.466189265375501</v>
+      </c>
+    </row>
+    <row r="15" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B15" t="str">
+        <f>lc_detailed!AM15</f>
+        <v>CA_TSC+CC90:H2</v>
+      </c>
+      <c r="C15" t="str">
+        <f>lc_detailed!AN15</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D15" s="21">
+        <f>lc_detailed!AU15/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="21">
+        <f>lc_detailed!AV15/$AM$3</f>
+        <v>-0.30639510581400747</v>
+      </c>
+      <c r="F15" s="21">
+        <f>lc_detailed!AW15/$AM$3</f>
+        <v>7.4521648560442966E-2</v>
+      </c>
+      <c r="G15" s="21">
+        <f>lc_detailed!AX15/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H15" s="21">
+        <f>lc_detailed!AY15/$AM$3</f>
+        <v>-0.17072840509347034</v>
+      </c>
+      <c r="I15" s="21">
+        <f>lc_detailed!AZ15/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="21">
+        <f>lc_detailed!BA15/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K15" s="21">
+        <f>lc_detailed!BB15/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L15" s="21">
+        <f>lc_detailed!BC15/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M15" s="21">
+        <f>lc_detailed!BE15/$AM$3</f>
+        <v>-1.6351444765381382</v>
+      </c>
+      <c r="N15" s="21">
+        <f>lc_detailed!BF15/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O15" s="21">
+        <f>lc_detailed!BD15</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P15" s="21">
+        <f>lc_detailed!AO15</f>
+        <v>837.83137619335605</v>
+      </c>
+      <c r="Q15" s="21">
+        <f t="shared" si="0"/>
+        <v>18.373495091959562</v>
+      </c>
+      <c r="R15" s="21">
+        <f t="shared" si="1"/>
+        <v>18.373495091959558</v>
+      </c>
+      <c r="T15" t="str">
+        <f>lc_detailed!AM15</f>
+        <v>CA_TSC+CC90:H2</v>
+      </c>
+      <c r="U15" t="str">
+        <f>lc_detailed!AN15</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V15" s="21">
+        <f>lc_detailed!AU15/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W15" s="21">
+        <f>lc_detailed!AV15/$AM$3</f>
+        <v>-0.30639510581400747</v>
+      </c>
+      <c r="X15" s="21">
+        <f>lc_detailed!AW15/$AM$3</f>
+        <v>7.4521648560442966E-2</v>
+      </c>
+      <c r="Y15" s="21">
+        <f>lc_detailed!AX15/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z15" s="21">
+        <f>lc_detailed!AY15/$AM$3</f>
+        <v>-0.17072840509347034</v>
+      </c>
+      <c r="AA15" s="21">
+        <f>lc_detailed!AZ15/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="21">
+        <f>lc_detailed!BA15/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC15" s="21">
+        <f>lc_detailed!BB15/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD15" s="21">
+        <f>lc_detailed!BC15/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE15" s="21">
+        <f>lc_detailed!BK15/$AM$3</f>
+        <v>-1.6351444765381382</v>
+      </c>
+      <c r="AF15" s="21">
+        <f>lc_detailed!BL15/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG15" s="21">
+        <f>lc_detailed!BJ15</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH15" s="21">
+        <f>lc_detailed!AR15</f>
+        <v>1212.5166312934516</v>
+      </c>
+      <c r="AI15" s="21">
+        <f t="shared" si="2"/>
+        <v>26.590277002049376</v>
+      </c>
+      <c r="AJ15" s="21">
+        <f t="shared" si="3"/>
+        <v>26.590277002049373</v>
+      </c>
+    </row>
+    <row r="16" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B16" t="str">
+        <f>lc_detailed!AM16</f>
+        <v>CA_TSC+H2in</v>
+      </c>
+      <c r="C16" t="str">
+        <f>lc_detailed!AN16</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D16" s="21">
+        <f>lc_detailed!AU16/$AM$3</f>
+        <v>4.2678727335815188E-2</v>
+      </c>
+      <c r="E16" s="21">
+        <f>lc_detailed!AV16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="21">
+        <f>lc_detailed!AW16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="21">
+        <f>lc_detailed!AX16/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H16" s="21">
+        <f>lc_detailed!AY16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="21">
+        <f>lc_detailed!AZ16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="21">
+        <f>lc_detailed!BA16/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K16" s="21">
+        <f>lc_detailed!BB16/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L16" s="21">
+        <f>lc_detailed!BC16/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M16" s="21">
+        <f>lc_detailed!BE16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="21">
+        <f>lc_detailed!BF16/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O16" s="21">
+        <f>lc_detailed!BD16</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P16" s="21">
+        <f>lc_detailed!AO16</f>
+        <v>856.56737502018268</v>
+      </c>
+      <c r="Q16" s="21">
+        <f t="shared" si="0"/>
+        <v>18.784372259214532</v>
+      </c>
+      <c r="R16" s="21">
+        <f t="shared" si="1"/>
+        <v>18.784372259214532</v>
+      </c>
+      <c r="T16" t="str">
+        <f>lc_detailed!AM16</f>
+        <v>CA_TSC+H2in</v>
+      </c>
+      <c r="U16" t="str">
+        <f>lc_detailed!AN16</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V16" s="21">
+        <f>lc_detailed!AU16/$AM$3</f>
+        <v>4.2678727335815188E-2</v>
+      </c>
+      <c r="W16" s="21">
+        <f>lc_detailed!AV16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X16" s="21">
+        <f>lc_detailed!AW16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="21">
+        <f>lc_detailed!AX16/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z16" s="21">
+        <f>lc_detailed!AY16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="21">
+        <f>lc_detailed!AZ16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="21">
+        <f>lc_detailed!BA16/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC16" s="21">
+        <f>lc_detailed!BB16/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD16" s="21">
+        <f>lc_detailed!BC16/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE16" s="21">
+        <f>lc_detailed!BK16/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="21">
+        <f>lc_detailed!BL16/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG16" s="21">
+        <f>lc_detailed!BJ16</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH16" s="21">
+        <f>lc_detailed!AR16</f>
+        <v>1231.25263012146</v>
+      </c>
+      <c r="AI16" s="21">
+        <f t="shared" si="2"/>
+        <v>27.001154169330263</v>
+      </c>
+      <c r="AJ16" s="21">
+        <f t="shared" si="3"/>
+        <v>27.001154169330263</v>
+      </c>
+    </row>
+    <row r="17" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B17" t="str">
+        <f>lc_detailed!AM17</f>
+        <v>CA_TSC+H2in:CH4</v>
+      </c>
+      <c r="C17" t="str">
+        <f>lc_detailed!AN17</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D17" s="21">
+        <f>lc_detailed!AU17/$AM$3</f>
+        <v>0.2637163786123633</v>
+      </c>
+      <c r="E17" s="21">
+        <f>lc_detailed!AV17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="21">
+        <f>lc_detailed!AW17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="21">
+        <f>lc_detailed!AX17/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H17" s="21">
+        <f>lc_detailed!AY17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="21">
+        <f>lc_detailed!AZ17/$AM$3</f>
+        <v>0.15299954696665649</v>
+      </c>
+      <c r="J17" s="21">
+        <f>lc_detailed!BA17/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K17" s="21">
+        <f>lc_detailed!BB17/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L17" s="21">
+        <f>lc_detailed!BC17/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M17" s="21">
+        <f>lc_detailed!BE17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="21">
+        <f>lc_detailed!BF17/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O17" s="21">
+        <f>lc_detailed!BD17</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P17" s="21">
+        <f>lc_detailed!AO17</f>
+        <v>873.62347127255873</v>
+      </c>
+      <c r="Q17" s="21">
+        <f t="shared" si="0"/>
+        <v>19.158409457731551</v>
+      </c>
+      <c r="R17" s="21">
+        <f t="shared" si="1"/>
+        <v>19.158409457731548</v>
+      </c>
+      <c r="T17" t="str">
+        <f>lc_detailed!AM17</f>
+        <v>CA_TSC+H2in:CH4</v>
+      </c>
+      <c r="U17" t="str">
+        <f>lc_detailed!AN17</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V17" s="21">
+        <f>lc_detailed!AU17/$AM$3</f>
+        <v>0.2637163786123633</v>
+      </c>
+      <c r="W17" s="21">
+        <f>lc_detailed!AV17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="21">
+        <f>lc_detailed!AW17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="21">
+        <f>lc_detailed!AX17/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z17" s="21">
+        <f>lc_detailed!AY17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="21">
+        <f>lc_detailed!AZ17/$AM$3</f>
+        <v>0.15299954696665649</v>
+      </c>
+      <c r="AB17" s="21">
+        <f>lc_detailed!BA17/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC17" s="21">
+        <f>lc_detailed!BB17/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD17" s="21">
+        <f>lc_detailed!BC17/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE17" s="21">
+        <f>lc_detailed!BK17/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="21">
+        <f>lc_detailed!BL17/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG17" s="21">
+        <f>lc_detailed!BJ17</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH17" s="21">
+        <f>lc_detailed!AR17</f>
+        <v>1248.3087263613502</v>
+      </c>
+      <c r="AI17" s="21">
+        <f t="shared" si="2"/>
+        <v>27.375191367573468</v>
+      </c>
+      <c r="AJ17" s="21">
+        <f t="shared" si="3"/>
+        <v>27.375191367573468</v>
+      </c>
+    </row>
+    <row r="18" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B18" t="str">
+        <f>lc_detailed!AM18</f>
+        <v>SW_TSC+CC90</v>
+      </c>
+      <c r="C18" t="str">
+        <f>lc_detailed!AN18</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D18" s="21">
+        <f>lc_detailed!AU18/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="21">
+        <f>lc_detailed!AV18/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="21">
+        <f>lc_detailed!AW18/$AM$3</f>
+        <v>6.680852938958344E-2</v>
+      </c>
+      <c r="G18" s="21">
+        <f>lc_detailed!AX18/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H18" s="21">
+        <f>lc_detailed!AY18/$AM$3</f>
+        <v>-1.1980339652309062E-2</v>
+      </c>
+      <c r="I18" s="21">
+        <f>lc_detailed!AZ18/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="21">
+        <f>lc_detailed!BA18/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K18" s="21">
+        <f>lc_detailed!BB18/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L18" s="21">
+        <f>lc_detailed!BC18/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M18" s="21">
+        <f>lc_detailed!BE18/$AM$3</f>
+        <v>-0.94164953110951999</v>
+      </c>
+      <c r="N18" s="21">
+        <f>lc_detailed!BF18/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O18" s="21">
+        <f>lc_detailed!BD18</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P18" s="21">
+        <f>lc_detailed!AO18</f>
+        <v>853.03548001548961</v>
+      </c>
+      <c r="Q18" s="21">
+        <f t="shared" si="0"/>
+        <v>18.706918421392317</v>
+      </c>
+      <c r="R18" s="21">
+        <f t="shared" si="1"/>
+        <v>18.706918421392313</v>
+      </c>
+      <c r="T18" t="str">
+        <f>lc_detailed!AM18</f>
+        <v>SW_TSC+CC90</v>
+      </c>
+      <c r="U18" t="str">
+        <f>lc_detailed!AN18</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V18" s="21">
+        <f>lc_detailed!AU18/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="21">
+        <f>lc_detailed!AV18/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="21">
+        <f>lc_detailed!AW18/$AM$3</f>
+        <v>6.680852938958344E-2</v>
+      </c>
+      <c r="Y18" s="21">
+        <f>lc_detailed!AX18/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z18" s="21">
+        <f>lc_detailed!AY18/$AM$3</f>
+        <v>-1.1980339652309062E-2</v>
+      </c>
+      <c r="AA18" s="21">
+        <f>lc_detailed!AZ18/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="21">
+        <f>lc_detailed!BA18/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC18" s="21">
+        <f>lc_detailed!BB18/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD18" s="21">
+        <f>lc_detailed!BC18/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE18" s="21">
+        <f>lc_detailed!BK18/$AM$3</f>
+        <v>-0.94164953110951999</v>
+      </c>
+      <c r="AF18" s="21">
+        <f>lc_detailed!BL18/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG18" s="21">
+        <f>lc_detailed!BJ18</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH18" s="21">
+        <f>lc_detailed!AR18</f>
+        <v>1227.7207351177231</v>
+      </c>
+      <c r="AI18" s="21">
+        <f t="shared" si="2"/>
+        <v>26.923700331529012</v>
+      </c>
+      <c r="AJ18" s="21">
+        <f t="shared" si="3"/>
+        <v>26.923700331529012</v>
+      </c>
+    </row>
+    <row r="19" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B19" t="str">
+        <f>lc_detailed!AM19</f>
+        <v>SW_TSC:H2</v>
+      </c>
+      <c r="C19" t="str">
+        <f>lc_detailed!AN19</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D19" s="21">
+        <f>lc_detailed!AU19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="21">
+        <f>lc_detailed!AV19/$AM$3</f>
+        <v>-0.41182630936364006</v>
+      </c>
+      <c r="F19" s="21">
+        <f>lc_detailed!AW19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="21">
+        <f>lc_detailed!AX19/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H19" s="21">
+        <f>lc_detailed!AY19/$AM$3</f>
+        <v>-6.9571690599876279E-2</v>
+      </c>
+      <c r="I19" s="21">
+        <f>lc_detailed!AZ19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="21">
+        <f>lc_detailed!BA19/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K19" s="21">
+        <f>lc_detailed!BB19/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L19" s="21">
+        <f>lc_detailed!BC19/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M19" s="21">
+        <f>lc_detailed!BE19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="21">
+        <f>lc_detailed!BF19/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O19" s="21">
+        <f>lc_detailed!BD19</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P19" s="21">
+        <f>lc_detailed!AO19</f>
+        <v>877.57805868501964</v>
+      </c>
+      <c r="Q19" s="21">
+        <f t="shared" si="0"/>
+        <v>19.245132865899553</v>
+      </c>
+      <c r="R19" s="21">
+        <f t="shared" si="1"/>
+        <v>19.245132865899553</v>
+      </c>
+      <c r="T19" t="str">
+        <f>lc_detailed!AM19</f>
+        <v>SW_TSC:H2</v>
+      </c>
+      <c r="U19" t="str">
+        <f>lc_detailed!AN19</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V19" s="21">
+        <f>lc_detailed!AU19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="21">
+        <f>lc_detailed!AV19/$AM$3</f>
+        <v>-0.41182630936364006</v>
+      </c>
+      <c r="X19" s="21">
+        <f>lc_detailed!AW19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="21">
+        <f>lc_detailed!AX19/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z19" s="21">
+        <f>lc_detailed!AY19/$AM$3</f>
+        <v>-6.9571690599876279E-2</v>
+      </c>
+      <c r="AA19" s="21">
+        <f>lc_detailed!AZ19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="21">
+        <f>lc_detailed!BA19/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC19" s="21">
+        <f>lc_detailed!BB19/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD19" s="21">
+        <f>lc_detailed!BC19/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE19" s="21">
+        <f>lc_detailed!BK19/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="21">
+        <f>lc_detailed!BL19/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG19" s="21">
+        <f>lc_detailed!BJ19</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH19" s="21">
+        <f>lc_detailed!AR19</f>
+        <v>1252.2633138001675</v>
+      </c>
+      <c r="AI19" s="21">
+        <f t="shared" si="2"/>
+        <v>27.46191477631946</v>
+      </c>
+      <c r="AJ19" s="21">
+        <f t="shared" si="3"/>
+        <v>27.46191477631946</v>
+      </c>
+    </row>
+    <row r="20" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B20" t="str">
+        <f>lc_detailed!AM20</f>
+        <v>SW_TSC+CC90:H2</v>
+      </c>
+      <c r="C20" t="str">
+        <f>lc_detailed!AN20</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D20" s="21">
+        <f>lc_detailed!AU20/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="21">
+        <f>lc_detailed!AV20/$AM$3</f>
+        <v>-0.41182630936364006</v>
+      </c>
+      <c r="F20" s="21">
+        <f>lc_detailed!AW20/$AM$3</f>
+        <v>7.7890265214513171E-2</v>
+      </c>
+      <c r="G20" s="21">
+        <f>lc_detailed!AX20/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H20" s="21">
+        <f>lc_detailed!AY20/$AM$3</f>
+        <v>-6.9571690599876279E-2</v>
+      </c>
+      <c r="I20" s="21">
+        <f>lc_detailed!AZ20/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <f>lc_detailed!BA20/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K20" s="21">
+        <f>lc_detailed!BB20/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L20" s="21">
+        <f>lc_detailed!BC20/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M20" s="21">
+        <f>lc_detailed!BE20/$AM$3</f>
+        <v>-1.6362950818907711</v>
+      </c>
+      <c r="N20" s="21">
+        <f>lc_detailed!BF20/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O20" s="21">
+        <f>lc_detailed!BD20</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P20" s="21">
+        <f>lc_detailed!AO20</f>
+        <v>837.73760080774616</v>
+      </c>
+      <c r="Q20" s="21">
+        <f t="shared" si="0"/>
+        <v>18.371438614204958</v>
+      </c>
+      <c r="R20" s="21">
+        <f t="shared" si="1"/>
+        <v>18.371438614204958</v>
+      </c>
+      <c r="T20" t="str">
+        <f>lc_detailed!AM20</f>
+        <v>SW_TSC+CC90:H2</v>
+      </c>
+      <c r="U20" t="str">
+        <f>lc_detailed!AN20</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V20" s="21">
+        <f>lc_detailed!AU20/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W20" s="21">
+        <f>lc_detailed!AV20/$AM$3</f>
+        <v>-0.41182630936364006</v>
+      </c>
+      <c r="X20" s="21">
+        <f>lc_detailed!AW20/$AM$3</f>
+        <v>7.7890265214513171E-2</v>
+      </c>
+      <c r="Y20" s="21">
+        <f>lc_detailed!AX20/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z20" s="21">
+        <f>lc_detailed!AY20/$AM$3</f>
+        <v>-6.9571690599876279E-2</v>
+      </c>
+      <c r="AA20" s="21">
+        <f>lc_detailed!AZ20/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="21">
+        <f>lc_detailed!BA20/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC20" s="21">
+        <f>lc_detailed!BB20/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD20" s="21">
+        <f>lc_detailed!BC20/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE20" s="21">
+        <f>lc_detailed!BK20/$AM$3</f>
+        <v>-1.6362950818907711</v>
+      </c>
+      <c r="AF20" s="21">
+        <f>lc_detailed!BL20/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG20" s="21">
+        <f>lc_detailed!BJ20</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH20" s="21">
+        <f>lc_detailed!AR20</f>
+        <v>1212.4228559078415</v>
+      </c>
+      <c r="AI20" s="21">
+        <f t="shared" si="2"/>
+        <v>26.588220524294769</v>
+      </c>
+      <c r="AJ20" s="21">
+        <f t="shared" si="3"/>
+        <v>26.588220524294773</v>
+      </c>
+    </row>
+    <row r="21" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
+        <f>lc_detailed!AM21</f>
+        <v>SW_TSC+H2in</v>
+      </c>
+      <c r="C21" t="str">
+        <f>lc_detailed!AN21</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D21" s="21">
+        <f>lc_detailed!AU21/$AM$3</f>
+        <v>5.7364567623724536E-2</v>
+      </c>
+      <c r="E21" s="21">
+        <f>lc_detailed!AV21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="21">
+        <f>lc_detailed!AW21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="21">
+        <f>lc_detailed!AX21/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H21" s="21">
+        <f>lc_detailed!AY21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="21">
+        <f>lc_detailed!AZ21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="21">
+        <f>lc_detailed!BA21/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K21" s="21">
+        <f>lc_detailed!BB21/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L21" s="21">
+        <f>lc_detailed!BC21/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M21" s="21">
+        <f>lc_detailed!BE21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="21">
+        <f>lc_detailed!BF21/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O21" s="21">
+        <f>lc_detailed!BD21</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P21" s="21">
+        <f>lc_detailed!AO21</f>
+        <v>857.23704933731142</v>
+      </c>
+      <c r="Q21" s="21">
+        <f t="shared" si="0"/>
+        <v>18.799058099502442</v>
+      </c>
+      <c r="R21" s="21">
+        <f t="shared" si="1"/>
+        <v>18.799058099502442</v>
+      </c>
+      <c r="T21" t="str">
+        <f>lc_detailed!AM21</f>
+        <v>SW_TSC+H2in</v>
+      </c>
+      <c r="U21" t="str">
+        <f>lc_detailed!AN21</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V21" s="21">
+        <f>lc_detailed!AU21/$AM$3</f>
+        <v>5.7364567623724536E-2</v>
+      </c>
+      <c r="W21" s="21">
+        <f>lc_detailed!AV21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="21">
+        <f>lc_detailed!AW21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="21">
+        <f>lc_detailed!AX21/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z21" s="21">
+        <f>lc_detailed!AY21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="21">
+        <f>lc_detailed!AZ21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="21">
+        <f>lc_detailed!BA21/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC21" s="21">
+        <f>lc_detailed!BB21/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD21" s="21">
+        <f>lc_detailed!BC21/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE21" s="21">
+        <f>lc_detailed!BK21/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="21">
+        <f>lc_detailed!BL21/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG21" s="21">
+        <f>lc_detailed!BJ21</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH21" s="21">
+        <f>lc_detailed!AR21</f>
+        <v>1231.9223044385888</v>
+      </c>
+      <c r="AI21" s="21">
+        <f t="shared" si="2"/>
+        <v>27.015840009618174</v>
+      </c>
+      <c r="AJ21" s="21">
+        <f t="shared" si="3"/>
+        <v>27.015840009618174</v>
+      </c>
+    </row>
+    <row r="22" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B22" t="str">
+        <f>lc_detailed!AM22</f>
+        <v>SW_TSC+H2in:CH4</v>
+      </c>
+      <c r="C22" t="str">
+        <f>lc_detailed!AN22</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D22" s="21">
+        <f>lc_detailed!AU22/$AM$3</f>
+        <v>0.35446174192025504</v>
+      </c>
+      <c r="E22" s="21">
+        <f>lc_detailed!AV22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="21">
+        <f>lc_detailed!AW22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="21">
+        <f>lc_detailed!AX22/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H22" s="21">
+        <f>lc_detailed!AY22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="21">
+        <f>lc_detailed!AZ22/$AM$3</f>
+        <v>6.2347194877488923E-2</v>
+      </c>
+      <c r="J22" s="21">
+        <f>lc_detailed!BA22/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K22" s="21">
+        <f>lc_detailed!BB22/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L22" s="21">
+        <f>lc_detailed!BC22/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M22" s="21">
+        <f>lc_detailed!BE22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="21">
+        <f>lc_detailed!BF22/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O22" s="21">
+        <f>lc_detailed!BD22</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P22" s="21">
+        <f>lc_detailed!AO22</f>
+        <v>873.62771258413261</v>
+      </c>
+      <c r="Q22" s="21">
+        <f t="shared" si="0"/>
+        <v>19.158502468950275</v>
+      </c>
+      <c r="R22" s="21">
+        <f t="shared" si="1"/>
+        <v>19.158502468950275</v>
+      </c>
+      <c r="T22" t="str">
+        <f>lc_detailed!AM22</f>
+        <v>SW_TSC+H2in:CH4</v>
+      </c>
+      <c r="U22" t="str">
+        <f>lc_detailed!AN22</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V22" s="21">
+        <f>lc_detailed!AU22/$AM$3</f>
+        <v>0.35446174192025504</v>
+      </c>
+      <c r="W22" s="21">
+        <f>lc_detailed!AV22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="21">
+        <f>lc_detailed!AW22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="21">
+        <f>lc_detailed!AX22/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z22" s="21">
+        <f>lc_detailed!AY22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="21">
+        <f>lc_detailed!AZ22/$AM$3</f>
+        <v>6.2347194877488923E-2</v>
+      </c>
+      <c r="AB22" s="21">
+        <f>lc_detailed!BA22/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC22" s="21">
+        <f>lc_detailed!BB22/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD22" s="21">
+        <f>lc_detailed!BC22/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE22" s="21">
+        <f>lc_detailed!BK22/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="21">
+        <f>lc_detailed!BL22/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG22" s="21">
+        <f>lc_detailed!BJ22</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH22" s="21">
+        <f>lc_detailed!AR22</f>
+        <v>1248.3129676729241</v>
+      </c>
+      <c r="AI22" s="21">
+        <f t="shared" si="2"/>
+        <v>27.375284378792195</v>
+      </c>
+      <c r="AJ22" s="21">
+        <f t="shared" si="3"/>
+        <v>27.375284378792195</v>
+      </c>
+    </row>
+    <row r="23" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B23" t="str">
+        <f>lc_detailed!AM23</f>
+        <v>NW_TSC+CC90</v>
+      </c>
+      <c r="C23" t="str">
+        <f>lc_detailed!AN23</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D23" s="21">
+        <f>lc_detailed!AU23/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="21">
+        <f>lc_detailed!AV23/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="21">
+        <f>lc_detailed!AW23/$AM$3</f>
+        <v>6.3435324477675623E-2</v>
+      </c>
+      <c r="G23" s="21">
+        <f>lc_detailed!AX23/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H23" s="21">
+        <f>lc_detailed!AY23/$AM$3</f>
+        <v>-2.2863492234672874E-2</v>
+      </c>
+      <c r="I23" s="21">
+        <f>lc_detailed!AZ23/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="21">
+        <f>lc_detailed!BA23/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K23" s="21">
+        <f>lc_detailed!BB23/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L23" s="21">
+        <f>lc_detailed!BC23/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M23" s="21">
+        <f>lc_detailed!BE23/$AM$3</f>
+        <v>-0.94205844624155199</v>
+      </c>
+      <c r="N23" s="21">
+        <f>lc_detailed!BF23/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O23" s="21">
+        <f>lc_detailed!BD23</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P23" s="21">
+        <f>lc_detailed!AO23</f>
+        <v>852.36674358373011</v>
+      </c>
+      <c r="Q23" s="21">
+        <f t="shared" si="0"/>
+        <v>18.69225314876601</v>
+      </c>
+      <c r="R23" s="21">
+        <f t="shared" si="1"/>
+        <v>18.692253148766007</v>
+      </c>
+      <c r="T23" t="str">
+        <f>lc_detailed!AM23</f>
+        <v>NW_TSC+CC90</v>
+      </c>
+      <c r="U23" t="str">
+        <f>lc_detailed!AN23</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V23" s="21">
+        <f>lc_detailed!AU23/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W23" s="21">
+        <f>lc_detailed!AV23/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X23" s="21">
+        <f>lc_detailed!AW23/$AM$3</f>
+        <v>6.3435324477675623E-2</v>
+      </c>
+      <c r="Y23" s="21">
+        <f>lc_detailed!AX23/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z23" s="21">
+        <f>lc_detailed!AY23/$AM$3</f>
+        <v>-2.2863492234672874E-2</v>
+      </c>
+      <c r="AA23" s="21">
+        <f>lc_detailed!AZ23/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="21">
+        <f>lc_detailed!BA23/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC23" s="21">
+        <f>lc_detailed!BB23/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD23" s="21">
+        <f>lc_detailed!BC23/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE23" s="21">
+        <f>lc_detailed!BK23/$AM$3</f>
+        <v>-0.94205844624155199</v>
+      </c>
+      <c r="AF23" s="21">
+        <f>lc_detailed!BL23/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG23" s="21">
+        <f>lc_detailed!BJ23</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH23" s="21">
+        <f>lc_detailed!AR23</f>
+        <v>1227.0519986859636</v>
+      </c>
+      <c r="AI23" s="21">
+        <f t="shared" si="2"/>
+        <v>26.90903505890271</v>
+      </c>
+      <c r="AJ23" s="21">
+        <f t="shared" si="3"/>
+        <v>26.909035058902706</v>
+      </c>
+    </row>
+    <row r="24" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B24" t="str">
+        <f>lc_detailed!AM24</f>
+        <v>NW_TSC:H2</v>
+      </c>
+      <c r="C24" t="str">
+        <f>lc_detailed!AN24</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D24" s="21">
+        <f>lc_detailed!AU24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="21">
+        <f>lc_detailed!AV24/$AM$3</f>
+        <v>-0.34583867569632065</v>
+      </c>
+      <c r="F24" s="21">
+        <f>lc_detailed!AW24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="21">
+        <f>lc_detailed!AX24/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H24" s="21">
+        <f>lc_detailed!AY24/$AM$3</f>
+        <v>-0.13277184570278494</v>
+      </c>
+      <c r="I24" s="21">
+        <f>lc_detailed!AZ24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="21">
+        <f>lc_detailed!BA24/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K24" s="21">
+        <f>lc_detailed!BB24/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L24" s="21">
+        <f>lc_detailed!BC24/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M24" s="21">
+        <f>lc_detailed!BE24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="21">
+        <f>lc_detailed!BF24/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O24" s="21">
+        <f>lc_detailed!BD24</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P24" s="21">
+        <f>lc_detailed!AO24</f>
+        <v>877.70516770755671</v>
+      </c>
+      <c r="Q24" s="21">
+        <f t="shared" si="0"/>
+        <v>19.247920344463964</v>
+      </c>
+      <c r="R24" s="21">
+        <f t="shared" si="1"/>
+        <v>19.247920344463964</v>
+      </c>
+      <c r="T24" t="str">
+        <f>lc_detailed!AM24</f>
+        <v>NW_TSC:H2</v>
+      </c>
+      <c r="U24" t="str">
+        <f>lc_detailed!AN24</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V24" s="21">
+        <f>lc_detailed!AU24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="21">
+        <f>lc_detailed!AV24/$AM$3</f>
+        <v>-0.34583867569632065</v>
+      </c>
+      <c r="X24" s="21">
+        <f>lc_detailed!AW24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="21">
+        <f>lc_detailed!AX24/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z24" s="21">
+        <f>lc_detailed!AY24/$AM$3</f>
+        <v>-0.13277184570278494</v>
+      </c>
+      <c r="AA24" s="21">
+        <f>lc_detailed!AZ24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="21">
+        <f>lc_detailed!BA24/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC24" s="21">
+        <f>lc_detailed!BB24/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD24" s="21">
+        <f>lc_detailed!BC24/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE24" s="21">
+        <f>lc_detailed!BK24/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="21">
+        <f>lc_detailed!BL24/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG24" s="21">
+        <f>lc_detailed!BJ24</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH24" s="21">
+        <f>lc_detailed!AR24</f>
+        <v>1252.3904228227045</v>
+      </c>
+      <c r="AI24" s="21">
+        <f t="shared" si="2"/>
+        <v>27.464702254883871</v>
+      </c>
+      <c r="AJ24" s="21">
+        <f t="shared" si="3"/>
+        <v>27.464702254883871</v>
+      </c>
+    </row>
+    <row r="25" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B25" t="str">
+        <f>lc_detailed!AM25</f>
+        <v>NW_TSC+CC90:H2</v>
+      </c>
+      <c r="C25" t="str">
+        <f>lc_detailed!AN25</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D25" s="21">
+        <f>lc_detailed!AU25/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="21">
+        <f>lc_detailed!AV25/$AM$3</f>
+        <v>-0.34583867569632065</v>
+      </c>
+      <c r="F25" s="21">
+        <f>lc_detailed!AW25/$AM$3</f>
+        <v>7.3957536450506525E-2</v>
+      </c>
+      <c r="G25" s="21">
+        <f>lc_detailed!AX25/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H25" s="21">
+        <f>lc_detailed!AY25/$AM$3</f>
+        <v>-0.13277184570278494</v>
+      </c>
+      <c r="I25" s="21">
+        <f>lc_detailed!AZ25/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="21">
+        <f>lc_detailed!BA25/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K25" s="21">
+        <f>lc_detailed!BB25/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L25" s="21">
+        <f>lc_detailed!BC25/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M25" s="21">
+        <f>lc_detailed!BE25/$AM$3</f>
+        <v>-1.6370056496735286</v>
+      </c>
+      <c r="N25" s="21">
+        <f>lc_detailed!BF25/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O25" s="21">
+        <f>lc_detailed!BD25</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P25" s="21">
+        <f>lc_detailed!AO25</f>
+        <v>837.65297550775085</v>
+      </c>
+      <c r="Q25" s="21">
+        <f t="shared" si="0"/>
+        <v>18.369582796222605</v>
+      </c>
+      <c r="R25" s="21">
+        <f t="shared" si="1"/>
+        <v>18.369582796222605</v>
+      </c>
+      <c r="T25" t="str">
+        <f>lc_detailed!AM25</f>
+        <v>NW_TSC+CC90:H2</v>
+      </c>
+      <c r="U25" t="str">
+        <f>lc_detailed!AN25</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V25" s="21">
+        <f>lc_detailed!AU25/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="21">
+        <f>lc_detailed!AV25/$AM$3</f>
+        <v>-0.34583867569632065</v>
+      </c>
+      <c r="X25" s="21">
+        <f>lc_detailed!AW25/$AM$3</f>
+        <v>7.3957536450506525E-2</v>
+      </c>
+      <c r="Y25" s="21">
+        <f>lc_detailed!AX25/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z25" s="21">
+        <f>lc_detailed!AY25/$AM$3</f>
+        <v>-0.13277184570278494</v>
+      </c>
+      <c r="AA25" s="21">
+        <f>lc_detailed!AZ25/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="21">
+        <f>lc_detailed!BA25/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC25" s="21">
+        <f>lc_detailed!BB25/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD25" s="21">
+        <f>lc_detailed!BC25/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE25" s="21">
+        <f>lc_detailed!BK25/$AM$3</f>
+        <v>-1.6370056496735286</v>
+      </c>
+      <c r="AF25" s="21">
+        <f>lc_detailed!BL25/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG25" s="21">
+        <f>lc_detailed!BJ25</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH25" s="21">
+        <f>lc_detailed!AR25</f>
+        <v>1212.3382306078463</v>
+      </c>
+      <c r="AI25" s="21">
+        <f t="shared" si="2"/>
+        <v>26.58636470631242</v>
+      </c>
+      <c r="AJ25" s="21">
+        <f t="shared" si="3"/>
+        <v>26.58636470631242</v>
+      </c>
+    </row>
+    <row r="26" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B26" t="str">
+        <f>lc_detailed!AM26</f>
+        <v>NW_TSC+H2in</v>
+      </c>
+      <c r="C26" t="str">
+        <f>lc_detailed!AN26</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D26" s="21">
+        <f>lc_detailed!AU26/$AM$3</f>
+        <v>4.8172944874591082E-2</v>
+      </c>
+      <c r="E26" s="21">
+        <f>lc_detailed!AV26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="21">
+        <f>lc_detailed!AW26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="21">
+        <f>lc_detailed!AX26/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H26" s="21">
+        <f>lc_detailed!AY26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="21">
+        <f>lc_detailed!AZ26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="21">
+        <f>lc_detailed!BA26/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K26" s="21">
+        <f>lc_detailed!BB26/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L26" s="21">
+        <f>lc_detailed!BC26/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M26" s="21">
+        <f>lc_detailed!BE26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="21">
+        <f>lc_detailed!BF26/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O26" s="21">
+        <f>lc_detailed!BD26</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P26" s="21">
+        <f>lc_detailed!AO26</f>
+        <v>856.8179113399508</v>
+      </c>
+      <c r="Q26" s="21">
+        <f t="shared" si="0"/>
+        <v>18.789866476753307</v>
+      </c>
+      <c r="R26" s="21">
+        <f t="shared" si="1"/>
+        <v>18.789866476753307</v>
+      </c>
+      <c r="T26" t="str">
+        <f>lc_detailed!AM26</f>
+        <v>NW_TSC+H2in</v>
+      </c>
+      <c r="U26" t="str">
+        <f>lc_detailed!AN26</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V26" s="21">
+        <f>lc_detailed!AU26/$AM$3</f>
+        <v>4.8172944874591082E-2</v>
+      </c>
+      <c r="W26" s="21">
+        <f>lc_detailed!AV26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X26" s="21">
+        <f>lc_detailed!AW26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="21">
+        <f>lc_detailed!AX26/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z26" s="21">
+        <f>lc_detailed!AY26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA26" s="21">
+        <f>lc_detailed!AZ26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB26" s="21">
+        <f>lc_detailed!BA26/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC26" s="21">
+        <f>lc_detailed!BB26/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD26" s="21">
+        <f>lc_detailed!BC26/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE26" s="21">
+        <f>lc_detailed!BK26/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF26" s="21">
+        <f>lc_detailed!BL26/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG26" s="21">
+        <f>lc_detailed!BJ26</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH26" s="21">
+        <f>lc_detailed!AR26</f>
+        <v>1231.5031664412281</v>
+      </c>
+      <c r="AI26" s="21">
+        <f t="shared" si="2"/>
+        <v>27.006648386869038</v>
+      </c>
+      <c r="AJ26" s="21">
+        <f t="shared" si="3"/>
+        <v>27.006648386869038</v>
+      </c>
+    </row>
+    <row r="27" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B27" t="str">
+        <f>lc_detailed!AM27</f>
+        <v>NW_TSC+H2in:CH4</v>
+      </c>
+      <c r="C27" t="str">
+        <f>lc_detailed!AN27</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D27" s="21">
+        <f>lc_detailed!AU27/$AM$3</f>
+        <v>0.297665730973173</v>
+      </c>
+      <c r="E27" s="21">
+        <f>lc_detailed!AV27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="21">
+        <f>lc_detailed!AW27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="21">
+        <f>lc_detailed!AX27/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H27" s="21">
+        <f>lc_detailed!AY27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="21">
+        <f>lc_detailed!AZ27/$AM$3</f>
+        <v>0.11898449019851967</v>
+      </c>
+      <c r="J27" s="21">
+        <f>lc_detailed!BA27/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K27" s="21">
+        <f>lc_detailed!BB27/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L27" s="21">
+        <f>lc_detailed!BC27/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M27" s="21">
+        <f>lc_detailed!BE27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="21">
+        <f>lc_detailed!BF27/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O27" s="21">
+        <f>lc_detailed!BD27</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P27" s="21">
+        <f>lc_detailed!AO27</f>
+        <v>873.62047515158463</v>
+      </c>
+      <c r="Q27" s="21">
+        <f t="shared" si="0"/>
+        <v>19.158343753324225</v>
+      </c>
+      <c r="R27" s="21">
+        <f t="shared" si="1"/>
+        <v>19.158343753324221</v>
+      </c>
+      <c r="T27" t="str">
+        <f>lc_detailed!AM27</f>
+        <v>NW_TSC+H2in:CH4</v>
+      </c>
+      <c r="U27" t="str">
+        <f>lc_detailed!AN27</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V27" s="21">
+        <f>lc_detailed!AU27/$AM$3</f>
+        <v>0.297665730973173</v>
+      </c>
+      <c r="W27" s="21">
+        <f>lc_detailed!AV27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X27" s="21">
+        <f>lc_detailed!AW27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="21">
+        <f>lc_detailed!AX27/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z27" s="21">
+        <f>lc_detailed!AY27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="21">
+        <f>lc_detailed!AZ27/$AM$3</f>
+        <v>0.11898449019851967</v>
+      </c>
+      <c r="AB27" s="21">
+        <f>lc_detailed!BA27/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC27" s="21">
+        <f>lc_detailed!BB27/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD27" s="21">
+        <f>lc_detailed!BC27/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE27" s="21">
+        <f>lc_detailed!BK27/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="21">
+        <f>lc_detailed!BL27/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG27" s="21">
+        <f>lc_detailed!BJ27</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH27" s="21">
+        <f>lc_detailed!AR27</f>
+        <v>1248.3057302403761</v>
+      </c>
+      <c r="AI27" s="21">
+        <f t="shared" si="2"/>
+        <v>27.375125663166141</v>
+      </c>
+      <c r="AJ27" s="21">
+        <f t="shared" si="3"/>
+        <v>27.375125663166141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B28" t="str">
+        <f>lc_detailed!AM28</f>
+        <v>TX_TSC+CC90</v>
+      </c>
+      <c r="C28" t="str">
+        <f>lc_detailed!AN28</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D28" s="21">
+        <f>lc_detailed!AU28/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="21">
+        <f>lc_detailed!AV28/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="21">
+        <f>lc_detailed!AW28/$AM$3</f>
+        <v>6.9701053208481759E-2</v>
+      </c>
+      <c r="G28" s="21">
+        <f>lc_detailed!AX28/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H28" s="21">
+        <f>lc_detailed!AY28/$AM$3</f>
+        <v>-1.388652757205903E-2</v>
+      </c>
+      <c r="I28" s="21">
+        <f>lc_detailed!AZ28/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="21">
+        <f>lc_detailed!BA28/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K28" s="21">
+        <f>lc_detailed!BB28/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L28" s="21">
+        <f>lc_detailed!BC28/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M28" s="21">
+        <f>lc_detailed!BE28/$AM$3</f>
+        <v>-0.94485860452547799</v>
+      </c>
+      <c r="N28" s="21">
+        <f>lc_detailed!BF28/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O28" s="21">
+        <f>lc_detailed!BD28</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P28" s="21">
+        <f>lc_detailed!AO28</f>
+        <v>852.93412318472315</v>
+      </c>
+      <c r="Q28" s="21">
+        <f t="shared" si="0"/>
+        <v>18.704695683875507</v>
+      </c>
+      <c r="R28" s="21">
+        <f t="shared" si="1"/>
+        <v>18.704695683875503</v>
+      </c>
+      <c r="T28" t="str">
+        <f>lc_detailed!AM28</f>
+        <v>TX_TSC+CC90</v>
+      </c>
+      <c r="U28" t="str">
+        <f>lc_detailed!AN28</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V28" s="21">
+        <f>lc_detailed!AU28/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W28" s="21">
+        <f>lc_detailed!AV28/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X28" s="21">
+        <f>lc_detailed!AW28/$AM$3</f>
+        <v>6.9701053208481759E-2</v>
+      </c>
+      <c r="Y28" s="21">
+        <f>lc_detailed!AX28/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z28" s="21">
+        <f>lc_detailed!AY28/$AM$3</f>
+        <v>-1.388652757205903E-2</v>
+      </c>
+      <c r="AA28" s="21">
+        <f>lc_detailed!AZ28/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB28" s="21">
+        <f>lc_detailed!BA28/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC28" s="21">
+        <f>lc_detailed!BB28/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD28" s="21">
+        <f>lc_detailed!BC28/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE28" s="21">
+        <f>lc_detailed!BK28/$AM$3</f>
+        <v>-0.94485860452547799</v>
+      </c>
+      <c r="AF28" s="21">
+        <f>lc_detailed!BL28/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG28" s="21">
+        <f>lc_detailed!BJ28</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH28" s="21">
+        <f>lc_detailed!AR28</f>
+        <v>1227.6193782869568</v>
+      </c>
+      <c r="AI28" s="21">
+        <f t="shared" si="2"/>
+        <v>26.92147759401221</v>
+      </c>
+      <c r="AJ28" s="21">
+        <f t="shared" si="3"/>
+        <v>26.921477594012202</v>
+      </c>
+    </row>
+    <row r="29" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B29" t="str">
+        <f>lc_detailed!AM29</f>
+        <v>TX_TSC:H2</v>
+      </c>
+      <c r="C29" t="str">
+        <f>lc_detailed!AN29</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D29" s="21">
+        <f>lc_detailed!AU29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="21">
+        <f>lc_detailed!AV29/$AM$3</f>
+        <v>-0.40004431463636292</v>
+      </c>
+      <c r="F29" s="21">
+        <f>lc_detailed!AW29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="21">
+        <f>lc_detailed!AX29/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H29" s="21">
+        <f>lc_detailed!AY29/$AM$3</f>
+        <v>-8.0641219513650136E-2</v>
+      </c>
+      <c r="I29" s="21">
+        <f>lc_detailed!AZ29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="21">
+        <f>lc_detailed!BA29/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K29" s="21">
+        <f>lc_detailed!BB29/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L29" s="21">
+        <f>lc_detailed!BC29/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M29" s="21">
+        <f>lc_detailed!BE29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="21">
+        <f>lc_detailed!BF29/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O29" s="21">
+        <f>lc_detailed!BD29</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P29" s="21">
+        <f>lc_detailed!AO29</f>
+        <v>877.61054712611531</v>
+      </c>
+      <c r="Q29" s="21">
+        <f t="shared" si="0"/>
+        <v>19.245845331713053</v>
+      </c>
+      <c r="R29" s="21">
+        <f t="shared" si="1"/>
+        <v>19.245845331713056</v>
+      </c>
+      <c r="T29" t="str">
+        <f>lc_detailed!AM29</f>
+        <v>TX_TSC:H2</v>
+      </c>
+      <c r="U29" t="str">
+        <f>lc_detailed!AN29</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V29" s="21">
+        <f>lc_detailed!AU29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W29" s="21">
+        <f>lc_detailed!AV29/$AM$3</f>
+        <v>-0.40004431463636292</v>
+      </c>
+      <c r="X29" s="21">
+        <f>lc_detailed!AW29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="21">
+        <f>lc_detailed!AX29/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z29" s="21">
+        <f>lc_detailed!AY29/$AM$3</f>
+        <v>-8.0641219513650136E-2</v>
+      </c>
+      <c r="AA29" s="21">
+        <f>lc_detailed!AZ29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB29" s="21">
+        <f>lc_detailed!BA29/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC29" s="21">
+        <f>lc_detailed!BB29/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD29" s="21">
+        <f>lc_detailed!BC29/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE29" s="21">
+        <f>lc_detailed!BK29/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="21">
+        <f>lc_detailed!BL29/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG29" s="21">
+        <f>lc_detailed!BJ29</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH29" s="21">
+        <f>lc_detailed!AR29</f>
+        <v>1252.2958022412631</v>
+      </c>
+      <c r="AI29" s="21">
+        <f t="shared" si="2"/>
+        <v>27.462627242132964</v>
+      </c>
+      <c r="AJ29" s="21">
+        <f t="shared" si="3"/>
+        <v>27.462627242132964</v>
+      </c>
+    </row>
+    <row r="30" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B30" t="str">
+        <f>lc_detailed!AM30</f>
+        <v>TX_TSC+CC90:H2</v>
+      </c>
+      <c r="C30" t="str">
+        <f>lc_detailed!AN30</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D30" s="21">
+        <f>lc_detailed!AU30/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="21">
+        <f>lc_detailed!AV30/$AM$3</f>
+        <v>-0.40004431463636292</v>
+      </c>
+      <c r="F30" s="21">
+        <f>lc_detailed!AW30/$AM$3</f>
+        <v>8.1262580837260803E-2</v>
+      </c>
+      <c r="G30" s="21">
+        <f>lc_detailed!AX30/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H30" s="21">
+        <f>lc_detailed!AY30/$AM$3</f>
+        <v>-8.0641219513650136E-2</v>
+      </c>
+      <c r="I30" s="21">
+        <f>lc_detailed!AZ30/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="21">
+        <f>lc_detailed!BA30/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K30" s="21">
+        <f>lc_detailed!BB30/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L30" s="21">
+        <f>lc_detailed!BC30/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M30" s="21">
+        <f>lc_detailed!BE30/$AM$3</f>
+        <v>-1.6418714570436073</v>
+      </c>
+      <c r="N30" s="21">
+        <f>lc_detailed!BF30/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O30" s="21">
+        <f>lc_detailed!BD30</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P30" s="21">
+        <f>lc_detailed!AO30</f>
+        <v>837.66958413426994</v>
+      </c>
+      <c r="Q30" s="21">
+        <f t="shared" si="0"/>
+        <v>18.369947020488375</v>
+      </c>
+      <c r="R30" s="21">
+        <f t="shared" si="1"/>
+        <v>18.369947020488372</v>
+      </c>
+      <c r="T30" t="str">
+        <f>lc_detailed!AM30</f>
+        <v>TX_TSC+CC90:H2</v>
+      </c>
+      <c r="U30" t="str">
+        <f>lc_detailed!AN30</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V30" s="21">
+        <f>lc_detailed!AU30/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W30" s="21">
+        <f>lc_detailed!AV30/$AM$3</f>
+        <v>-0.40004431463636292</v>
+      </c>
+      <c r="X30" s="21">
+        <f>lc_detailed!AW30/$AM$3</f>
+        <v>8.1262580837260803E-2</v>
+      </c>
+      <c r="Y30" s="21">
+        <f>lc_detailed!AX30/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z30" s="21">
+        <f>lc_detailed!AY30/$AM$3</f>
+        <v>-8.0641219513650136E-2</v>
+      </c>
+      <c r="AA30" s="21">
+        <f>lc_detailed!AZ30/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB30" s="21">
+        <f>lc_detailed!BA30/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC30" s="21">
+        <f>lc_detailed!BB30/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD30" s="21">
+        <f>lc_detailed!BC30/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE30" s="21">
+        <f>lc_detailed!BK30/$AM$3</f>
+        <v>-1.6418714570436073</v>
+      </c>
+      <c r="AF30" s="21">
+        <f>lc_detailed!BL30/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG30" s="21">
+        <f>lc_detailed!BJ30</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH30" s="21">
+        <f>lc_detailed!AR30</f>
+        <v>1212.3548392343655</v>
+      </c>
+      <c r="AI30" s="21">
+        <f t="shared" si="2"/>
+        <v>26.58672893057819</v>
+      </c>
+      <c r="AJ30" s="21">
+        <f t="shared" si="3"/>
+        <v>26.586728930578186</v>
+      </c>
+    </row>
+    <row r="31" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B31" t="str">
+        <f>lc_detailed!AM31</f>
+        <v>TX_TSC+H2in</v>
+      </c>
+      <c r="C31" t="str">
+        <f>lc_detailed!AN31</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D31" s="21">
+        <f>lc_detailed!AU31/$AM$3</f>
+        <v>5.5723416930075022E-2</v>
+      </c>
+      <c r="E31" s="21">
+        <f>lc_detailed!AV31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="21">
+        <f>lc_detailed!AW31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="21">
+        <f>lc_detailed!AX31/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H31" s="21">
+        <f>lc_detailed!AY31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="21">
+        <f>lc_detailed!AZ31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="21">
+        <f>lc_detailed!BA31/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K31" s="21">
+        <f>lc_detailed!BB31/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L31" s="21">
+        <f>lc_detailed!BC31/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M31" s="21">
+        <f>lc_detailed!BE31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="21">
+        <f>lc_detailed!BF31/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O31" s="21">
+        <f>lc_detailed!BD31</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P31" s="21">
+        <f>lc_detailed!AO31</f>
+        <v>857.16221286568089</v>
+      </c>
+      <c r="Q31" s="21">
+        <f t="shared" si="0"/>
+        <v>18.797416948808792</v>
+      </c>
+      <c r="R31" s="21">
+        <f t="shared" si="1"/>
+        <v>18.797416948808792</v>
+      </c>
+      <c r="T31" t="str">
+        <f>lc_detailed!AM31</f>
+        <v>TX_TSC+H2in</v>
+      </c>
+      <c r="U31" t="str">
+        <f>lc_detailed!AN31</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V31" s="21">
+        <f>lc_detailed!AU31/$AM$3</f>
+        <v>5.5723416930075022E-2</v>
+      </c>
+      <c r="W31" s="21">
+        <f>lc_detailed!AV31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X31" s="21">
+        <f>lc_detailed!AW31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="21">
+        <f>lc_detailed!AX31/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z31" s="21">
+        <f>lc_detailed!AY31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA31" s="21">
+        <f>lc_detailed!AZ31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB31" s="21">
+        <f>lc_detailed!BA31/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC31" s="21">
+        <f>lc_detailed!BB31/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD31" s="21">
+        <f>lc_detailed!BC31/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE31" s="21">
+        <f>lc_detailed!BK31/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF31" s="21">
+        <f>lc_detailed!BL31/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG31" s="21">
+        <f>lc_detailed!BJ31</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH31" s="21">
+        <f>lc_detailed!AR31</f>
+        <v>1231.8474679669582</v>
+      </c>
+      <c r="AI31" s="21">
+        <f t="shared" si="2"/>
+        <v>27.014198858924523</v>
+      </c>
+      <c r="AJ31" s="21">
+        <f t="shared" si="3"/>
+        <v>27.014198858924523</v>
+      </c>
+    </row>
+    <row r="32" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B32" t="str">
+        <f>lc_detailed!AM32</f>
+        <v>TX_TSC+H2in:CH4</v>
+      </c>
+      <c r="C32" t="str">
+        <f>lc_detailed!AN32</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D32" s="21">
+        <f>lc_detailed!AU32/$AM$3</f>
+        <v>0.34432089788146808</v>
+      </c>
+      <c r="E32" s="21">
+        <f>lc_detailed!AV32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="21">
+        <f>lc_detailed!AW32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="21">
+        <f>lc_detailed!AX32/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H32" s="21">
+        <f>lc_detailed!AY32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="21">
+        <f>lc_detailed!AZ32/$AM$3</f>
+        <v>7.2267236642152941E-2</v>
+      </c>
+      <c r="J32" s="21">
+        <f>lc_detailed!BA32/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K32" s="21">
+        <f>lc_detailed!BB32/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L32" s="21">
+        <f>lc_detailed!BC32/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M32" s="21">
+        <f>lc_detailed!BE32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="21">
+        <f>lc_detailed!BF32/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O32" s="21">
+        <f>lc_detailed!BD32</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P32" s="21">
+        <f>lc_detailed!AO32</f>
+        <v>873.61764400043251</v>
+      </c>
+      <c r="Q32" s="21">
+        <f t="shared" si="0"/>
+        <v>19.15828166667615</v>
+      </c>
+      <c r="R32" s="21">
+        <f t="shared" si="1"/>
+        <v>19.15828166667615</v>
+      </c>
+      <c r="T32" t="str">
+        <f>lc_detailed!AM32</f>
+        <v>TX_TSC+H2in:CH4</v>
+      </c>
+      <c r="U32" t="str">
+        <f>lc_detailed!AN32</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V32" s="21">
+        <f>lc_detailed!AU32/$AM$3</f>
+        <v>0.34432089788146808</v>
+      </c>
+      <c r="W32" s="21">
+        <f>lc_detailed!AV32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X32" s="21">
+        <f>lc_detailed!AW32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="21">
+        <f>lc_detailed!AX32/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z32" s="21">
+        <f>lc_detailed!AY32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA32" s="21">
+        <f>lc_detailed!AZ32/$AM$3</f>
+        <v>7.2267236642152941E-2</v>
+      </c>
+      <c r="AB32" s="21">
+        <f>lc_detailed!BA32/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC32" s="21">
+        <f>lc_detailed!BB32/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD32" s="21">
+        <f>lc_detailed!BC32/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE32" s="21">
+        <f>lc_detailed!BK32/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF32" s="21">
+        <f>lc_detailed!BL32/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG32" s="21">
+        <f>lc_detailed!BJ32</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH32" s="21">
+        <f>lc_detailed!AR32</f>
+        <v>1248.302899089224</v>
+      </c>
+      <c r="AI32" s="21">
+        <f t="shared" si="2"/>
+        <v>27.37506357651807</v>
+      </c>
+      <c r="AJ32" s="21">
+        <f t="shared" si="3"/>
+        <v>27.37506357651807</v>
+      </c>
+    </row>
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B33" t="str">
+        <f>lc_detailed!AM33</f>
+        <v>NCEN_TSC+CC90</v>
+      </c>
+      <c r="C33" t="str">
+        <f>lc_detailed!AN33</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D33" s="21">
+        <f>lc_detailed!AU33/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="21">
+        <f>lc_detailed!AV33/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="21">
+        <f>lc_detailed!AW33/$AM$3</f>
+        <v>7.3620445215287919E-2</v>
+      </c>
+      <c r="G33" s="21">
+        <f>lc_detailed!AX33/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H33" s="21">
+        <f>lc_detailed!AY33/$AM$3</f>
+        <v>-7.7325109559540734E-3</v>
+      </c>
+      <c r="I33" s="21">
+        <f>lc_detailed!AZ33/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="21">
+        <f>lc_detailed!BA33/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K33" s="21">
+        <f>lc_detailed!BB33/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L33" s="21">
+        <f>lc_detailed!BC33/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M33" s="21">
+        <f>lc_detailed!BE33/$AM$3</f>
+        <v>-0.93400815294148254</v>
+      </c>
+      <c r="N33" s="21">
+        <f>lc_detailed!BF33/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O33" s="21">
+        <f>lc_detailed!BD33</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P33" s="21">
+        <f>lc_detailed!AO33</f>
+        <v>853.88825121015816</v>
+      </c>
+      <c r="Q33" s="21">
+        <f t="shared" si="0"/>
+        <v>18.725619544082416</v>
+      </c>
+      <c r="R33" s="21">
+        <f t="shared" si="1"/>
+        <v>18.725619544082409</v>
+      </c>
+      <c r="T33" t="str">
+        <f>lc_detailed!AM33</f>
+        <v>NCEN_TSC+CC90</v>
+      </c>
+      <c r="U33" t="str">
+        <f>lc_detailed!AN33</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V33" s="21">
+        <f>lc_detailed!AU33/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W33" s="21">
+        <f>lc_detailed!AV33/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X33" s="21">
+        <f>lc_detailed!AW33/$AM$3</f>
+        <v>7.3620445215287919E-2</v>
+      </c>
+      <c r="Y33" s="21">
+        <f>lc_detailed!AX33/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z33" s="21">
+        <f>lc_detailed!AY33/$AM$3</f>
+        <v>-7.7325109559540734E-3</v>
+      </c>
+      <c r="AA33" s="21">
+        <f>lc_detailed!AZ33/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB33" s="21">
+        <f>lc_detailed!BA33/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC33" s="21">
+        <f>lc_detailed!BB33/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD33" s="21">
+        <f>lc_detailed!BC33/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE33" s="21">
+        <f>lc_detailed!BK33/$AM$3</f>
+        <v>-0.93400815294148254</v>
+      </c>
+      <c r="AF33" s="21">
+        <f>lc_detailed!BL33/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG33" s="21">
+        <f>lc_detailed!BJ33</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH33" s="21">
+        <f>lc_detailed!AR33</f>
+        <v>1228.5735063123916</v>
+      </c>
+      <c r="AI33" s="21">
+        <f t="shared" si="2"/>
+        <v>26.942401454219112</v>
+      </c>
+      <c r="AJ33" s="21">
+        <f t="shared" si="3"/>
+        <v>26.942401454219109</v>
+      </c>
+    </row>
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B34" t="str">
+        <f>lc_detailed!AM34</f>
+        <v>NCEN_TSC:H2</v>
+      </c>
+      <c r="C34" t="str">
+        <f>lc_detailed!AN34</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D34" s="21">
+        <f>lc_detailed!AU34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="21">
+        <f>lc_detailed!AV34/$AM$3</f>
+        <v>-0.44900706395587092</v>
+      </c>
+      <c r="F34" s="21">
+        <f>lc_detailed!AW34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="21">
+        <f>lc_detailed!AX34/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H34" s="21">
+        <f>lc_detailed!AY34/$AM$3</f>
+        <v>-4.4903890490625993E-2</v>
+      </c>
+      <c r="I34" s="21">
+        <f>lc_detailed!AZ34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="21">
+        <f>lc_detailed!BA34/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K34" s="21">
+        <f>lc_detailed!BB34/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L34" s="21">
+        <f>lc_detailed!BC34/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M34" s="21">
+        <f>lc_detailed!BE34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="21">
+        <f>lc_detailed!BF34/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O34" s="21">
+        <f>lc_detailed!BD34</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P34" s="21">
+        <f>lc_detailed!AO34</f>
+        <v>877.0074679605957</v>
+      </c>
+      <c r="Q34" s="21">
+        <f t="shared" si="0"/>
+        <v>19.23261991141657</v>
+      </c>
+      <c r="R34" s="21">
+        <f t="shared" si="1"/>
+        <v>19.23261991141657</v>
+      </c>
+      <c r="T34" t="str">
+        <f>lc_detailed!AM34</f>
+        <v>NCEN_TSC:H2</v>
+      </c>
+      <c r="U34" t="str">
+        <f>lc_detailed!AN34</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V34" s="21">
+        <f>lc_detailed!AU34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="21">
+        <f>lc_detailed!AV34/$AM$3</f>
+        <v>-0.44900706395587092</v>
+      </c>
+      <c r="X34" s="21">
+        <f>lc_detailed!AW34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="21">
+        <f>lc_detailed!AX34/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z34" s="21">
+        <f>lc_detailed!AY34/$AM$3</f>
+        <v>-4.4903890490625993E-2</v>
+      </c>
+      <c r="AA34" s="21">
+        <f>lc_detailed!AZ34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB34" s="21">
+        <f>lc_detailed!BA34/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC34" s="21">
+        <f>lc_detailed!BB34/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD34" s="21">
+        <f>lc_detailed!BC34/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE34" s="21">
+        <f>lc_detailed!BK34/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF34" s="21">
+        <f>lc_detailed!BL34/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG34" s="21">
+        <f>lc_detailed!BJ34</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH34" s="21">
+        <f>lc_detailed!AR34</f>
+        <v>1251.6927230757435</v>
+      </c>
+      <c r="AI34" s="21">
+        <f t="shared" si="2"/>
+        <v>27.449401821836481</v>
+      </c>
+      <c r="AJ34" s="21">
+        <f t="shared" si="3"/>
+        <v>27.449401821836478</v>
+      </c>
+    </row>
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B35" t="str">
+        <f>lc_detailed!AM35</f>
+        <v>NCEN_TSC+CC90:H2</v>
+      </c>
+      <c r="C35" t="str">
+        <f>lc_detailed!AN35</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D35" s="21">
+        <f>lc_detailed!AU35/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="21">
+        <f>lc_detailed!AV35/$AM$3</f>
+        <v>-0.44900706395587092</v>
+      </c>
+      <c r="F35" s="21">
+        <f>lc_detailed!AW35/$AM$3</f>
+        <v>8.5832094426005853E-2</v>
+      </c>
+      <c r="G35" s="21">
+        <f>lc_detailed!AX35/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H35" s="21">
+        <f>lc_detailed!AY35/$AM$3</f>
+        <v>-4.4903890490625993E-2</v>
+      </c>
+      <c r="I35" s="21">
+        <f>lc_detailed!AZ35/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="21">
+        <f>lc_detailed!BA35/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K35" s="21">
+        <f>lc_detailed!BB35/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L35" s="21">
+        <f>lc_detailed!BC35/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M35" s="21">
+        <f>lc_detailed!BE35/$AM$3</f>
+        <v>-1.6230167345841098</v>
+      </c>
+      <c r="N35" s="21">
+        <f>lc_detailed!BF35/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O35" s="21">
+        <f>lc_detailed!BD35</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P35" s="21">
+        <f>lc_detailed!AO35</f>
+        <v>838.13465013255006</v>
+      </c>
+      <c r="Q35" s="21">
+        <f t="shared" si="0"/>
+        <v>18.380145836240132</v>
+      </c>
+      <c r="R35" s="21">
+        <f t="shared" si="1"/>
+        <v>18.380145836240132</v>
+      </c>
+      <c r="T35" t="str">
+        <f>lc_detailed!AM35</f>
+        <v>NCEN_TSC+CC90:H2</v>
+      </c>
+      <c r="U35" t="str">
+        <f>lc_detailed!AN35</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V35" s="21">
+        <f>lc_detailed!AU35/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W35" s="21">
+        <f>lc_detailed!AV35/$AM$3</f>
+        <v>-0.44900706395587092</v>
+      </c>
+      <c r="X35" s="21">
+        <f>lc_detailed!AW35/$AM$3</f>
+        <v>8.5832094426005853E-2</v>
+      </c>
+      <c r="Y35" s="21">
+        <f>lc_detailed!AX35/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z35" s="21">
+        <f>lc_detailed!AY35/$AM$3</f>
+        <v>-4.4903890490625993E-2</v>
+      </c>
+      <c r="AA35" s="21">
+        <f>lc_detailed!AZ35/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB35" s="21">
+        <f>lc_detailed!BA35/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC35" s="21">
+        <f>lc_detailed!BB35/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD35" s="21">
+        <f>lc_detailed!BC35/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE35" s="21">
+        <f>lc_detailed!BK35/$AM$3</f>
+        <v>-1.6230167345841098</v>
+      </c>
+      <c r="AF35" s="21">
+        <f>lc_detailed!BL35/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG35" s="21">
+        <f>lc_detailed!BJ35</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH35" s="21">
+        <f>lc_detailed!AR35</f>
+        <v>1212.8199052326454</v>
+      </c>
+      <c r="AI35" s="21">
+        <f t="shared" si="2"/>
+        <v>26.596927746329943</v>
+      </c>
+      <c r="AJ35" s="21">
+        <f t="shared" si="3"/>
+        <v>26.596927746329946</v>
+      </c>
+    </row>
+    <row r="36" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B36" t="str">
+        <f>lc_detailed!AM36</f>
+        <v>NCEN_TSC+H2in</v>
+      </c>
+      <c r="C36" t="str">
+        <f>lc_detailed!AN36</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D36" s="21">
+        <f>lc_detailed!AU36/$AM$3</f>
+        <v>6.2543590582220934E-2</v>
+      </c>
+      <c r="E36" s="21">
+        <f>lc_detailed!AV36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="21">
+        <f>lc_detailed!AW36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="21">
+        <f>lc_detailed!AX36/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H36" s="21">
+        <f>lc_detailed!AY36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="21">
+        <f>lc_detailed!AZ36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="21">
+        <f>lc_detailed!BA36/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K36" s="21">
+        <f>lc_detailed!BB36/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L36" s="21">
+        <f>lc_detailed!BC36/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M36" s="21">
+        <f>lc_detailed!BE36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="21">
+        <f>lc_detailed!BF36/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O36" s="21">
+        <f>lc_detailed!BD36</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P36" s="21">
+        <f>lc_detailed!AO36</f>
+        <v>857.47321278421873</v>
+      </c>
+      <c r="Q36" s="21">
+        <f t="shared" si="0"/>
+        <v>18.804237122460936</v>
+      </c>
+      <c r="R36" s="21">
+        <f t="shared" si="1"/>
+        <v>18.80423712246094</v>
+      </c>
+      <c r="T36" t="str">
+        <f>lc_detailed!AM36</f>
+        <v>NCEN_TSC+H2in</v>
+      </c>
+      <c r="U36" t="str">
+        <f>lc_detailed!AN36</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V36" s="21">
+        <f>lc_detailed!AU36/$AM$3</f>
+        <v>6.2543590582220934E-2</v>
+      </c>
+      <c r="W36" s="21">
+        <f>lc_detailed!AV36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X36" s="21">
+        <f>lc_detailed!AW36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="21">
+        <f>lc_detailed!AX36/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z36" s="21">
+        <f>lc_detailed!AY36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA36" s="21">
+        <f>lc_detailed!AZ36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB36" s="21">
+        <f>lc_detailed!BA36/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC36" s="21">
+        <f>lc_detailed!BB36/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD36" s="21">
+        <f>lc_detailed!BC36/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE36" s="21">
+        <f>lc_detailed!BK36/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF36" s="21">
+        <f>lc_detailed!BL36/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG36" s="21">
+        <f>lc_detailed!BJ36</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH36" s="21">
+        <f>lc_detailed!AR36</f>
+        <v>1232.1584678854961</v>
+      </c>
+      <c r="AI36" s="21">
+        <f t="shared" si="2"/>
+        <v>27.021019032576667</v>
+      </c>
+      <c r="AJ36" s="21">
+        <f t="shared" si="3"/>
+        <v>27.021019032576671</v>
+      </c>
+    </row>
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B37" t="str">
+        <f>lc_detailed!AM37</f>
+        <v>NCEN_TSC+H2in:CH4</v>
+      </c>
+      <c r="C37" t="str">
+        <f>lc_detailed!AN37</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D37" s="21">
+        <f>lc_detailed!AU37/$AM$3</f>
+        <v>0.386463473570271</v>
+      </c>
+      <c r="E37" s="21">
+        <f>lc_detailed!AV37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="21">
+        <f>lc_detailed!AW37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="21">
+        <f>lc_detailed!AX37/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H37" s="21">
+        <f>lc_detailed!AY37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="21">
+        <f>lc_detailed!AZ37/$AM$3</f>
+        <v>4.0240959893843069E-2</v>
+      </c>
+      <c r="J37" s="21">
+        <f>lc_detailed!BA37/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K37" s="21">
+        <f>lc_detailed!BB37/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L37" s="21">
+        <f>lc_detailed!BC37/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M37" s="21">
+        <f>lc_detailed!BE37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="21">
+        <f>lc_detailed!BF37/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O37" s="21">
+        <f>lc_detailed!BD37</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P37" s="21">
+        <f>lc_detailed!AO37</f>
+        <v>874.07894723211905</v>
+      </c>
+      <c r="Q37" s="21">
+        <f t="shared" si="0"/>
+        <v>19.168397965616645</v>
+      </c>
+      <c r="R37" s="21">
+        <f t="shared" si="1"/>
+        <v>19.168397965616641</v>
+      </c>
+      <c r="T37" t="str">
+        <f>lc_detailed!AM37</f>
+        <v>NCEN_TSC+H2in:CH4</v>
+      </c>
+      <c r="U37" t="str">
+        <f>lc_detailed!AN37</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V37" s="21">
+        <f>lc_detailed!AU37/$AM$3</f>
+        <v>0.386463473570271</v>
+      </c>
+      <c r="W37" s="21">
+        <f>lc_detailed!AV37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X37" s="21">
+        <f>lc_detailed!AW37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="21">
+        <f>lc_detailed!AX37/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z37" s="21">
+        <f>lc_detailed!AY37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA37" s="21">
+        <f>lc_detailed!AZ37/$AM$3</f>
+        <v>4.0240959893843069E-2</v>
+      </c>
+      <c r="AB37" s="21">
+        <f>lc_detailed!BA37/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC37" s="21">
+        <f>lc_detailed!BB37/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD37" s="21">
+        <f>lc_detailed!BC37/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE37" s="21">
+        <f>lc_detailed!BK37/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF37" s="21">
+        <f>lc_detailed!BL37/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG37" s="21">
+        <f>lc_detailed!BJ37</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH37" s="21">
+        <f>lc_detailed!AR37</f>
+        <v>1248.7642023209105</v>
+      </c>
+      <c r="AI37" s="21">
+        <f t="shared" si="2"/>
+        <v>27.385179875458562</v>
+      </c>
+      <c r="AJ37" s="21">
+        <f t="shared" si="3"/>
+        <v>27.385179875458562</v>
+      </c>
+    </row>
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B38" t="str">
+        <f>lc_detailed!AM38</f>
+        <v>CEN_TSC+CC90</v>
+      </c>
+      <c r="C38" t="str">
+        <f>lc_detailed!AN38</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D38" s="21">
+        <f>lc_detailed!AU38/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="21">
+        <f>lc_detailed!AV38/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="21">
+        <f>lc_detailed!AW38/$AM$3</f>
+        <v>7.1605037349995099E-2</v>
+      </c>
+      <c r="G38" s="21">
+        <f>lc_detailed!AX38/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H38" s="21">
+        <f>lc_detailed!AY38/$AM$3</f>
+        <v>-1.3420286350359913E-2</v>
+      </c>
+      <c r="I38" s="21">
+        <f>lc_detailed!AZ38/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="21">
+        <f>lc_detailed!BA38/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K38" s="21">
+        <f>lc_detailed!BB38/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L38" s="21">
+        <f>lc_detailed!BC38/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M38" s="21">
+        <f>lc_detailed!BE38/$AM$3</f>
+        <v>-0.93292475730075397</v>
+      </c>
+      <c r="N38" s="21">
+        <f>lc_detailed!BF38/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O38" s="21">
+        <f>lc_detailed!BD38</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P38" s="21">
+        <f>lc_detailed!AO38</f>
+        <v>853.58638889473309</v>
+      </c>
+      <c r="Q38" s="21">
+        <f t="shared" si="0"/>
+        <v>18.718999756463443</v>
+      </c>
+      <c r="R38" s="21">
+        <f t="shared" si="1"/>
+        <v>18.71899975646344</v>
+      </c>
+      <c r="T38" t="str">
+        <f>lc_detailed!AM38</f>
+        <v>CEN_TSC+CC90</v>
+      </c>
+      <c r="U38" t="str">
+        <f>lc_detailed!AN38</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V38" s="21">
+        <f>lc_detailed!AU38/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="21">
+        <f>lc_detailed!AV38/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="21">
+        <f>lc_detailed!AW38/$AM$3</f>
+        <v>7.1605037349995099E-2</v>
+      </c>
+      <c r="Y38" s="21">
+        <f>lc_detailed!AX38/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z38" s="21">
+        <f>lc_detailed!AY38/$AM$3</f>
+        <v>-1.3420286350359913E-2</v>
+      </c>
+      <c r="AA38" s="21">
+        <f>lc_detailed!AZ38/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB38" s="21">
+        <f>lc_detailed!BA38/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC38" s="21">
+        <f>lc_detailed!BB38/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD38" s="21">
+        <f>lc_detailed!BC38/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE38" s="21">
+        <f>lc_detailed!BK38/$AM$3</f>
+        <v>-0.93292475730075397</v>
+      </c>
+      <c r="AF38" s="21">
+        <f>lc_detailed!BL38/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG38" s="21">
+        <f>lc_detailed!BJ38</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH38" s="21">
+        <f>lc_detailed!AR38</f>
+        <v>1228.2716439969668</v>
+      </c>
+      <c r="AI38" s="21">
+        <f t="shared" si="2"/>
+        <v>26.935781666600146</v>
+      </c>
+      <c r="AJ38" s="21">
+        <f t="shared" si="3"/>
+        <v>26.935781666600139</v>
+      </c>
+    </row>
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B39" t="str">
+        <f>lc_detailed!AM39</f>
+        <v>CEN_TSC:H2</v>
+      </c>
+      <c r="C39" t="str">
+        <f>lc_detailed!AN39</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D39" s="21">
+        <f>lc_detailed!AU39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="21">
+        <f>lc_detailed!AV39/$AM$3</f>
+        <v>-0.41514095054329514</v>
+      </c>
+      <c r="F39" s="21">
+        <f>lc_detailed!AW39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="21">
+        <f>lc_detailed!AX39/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H39" s="21">
+        <f>lc_detailed!AY39/$AM$3</f>
+        <v>-7.7933684421795935E-2</v>
+      </c>
+      <c r="I39" s="21">
+        <f>lc_detailed!AZ39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="21">
+        <f>lc_detailed!BA39/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K39" s="21">
+        <f>lc_detailed!BB39/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L39" s="21">
+        <f>lc_detailed!BC39/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M39" s="21">
+        <f>lc_detailed!BE39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="21">
+        <f>lc_detailed!BF39/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O39" s="21">
+        <f>lc_detailed!BD39</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P39" s="21">
+        <f>lc_detailed!AO39</f>
+        <v>877.04560412894784</v>
+      </c>
+      <c r="Q39" s="21">
+        <f t="shared" si="0"/>
+        <v>19.233456230897978</v>
+      </c>
+      <c r="R39" s="21">
+        <f t="shared" si="1"/>
+        <v>19.233456230897978</v>
+      </c>
+      <c r="T39" t="str">
+        <f>lc_detailed!AM39</f>
+        <v>CEN_TSC:H2</v>
+      </c>
+      <c r="U39" t="str">
+        <f>lc_detailed!AN39</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V39" s="21">
+        <f>lc_detailed!AU39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W39" s="21">
+        <f>lc_detailed!AV39/$AM$3</f>
+        <v>-0.41514095054329514</v>
+      </c>
+      <c r="X39" s="21">
+        <f>lc_detailed!AW39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="21">
+        <f>lc_detailed!AX39/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z39" s="21">
+        <f>lc_detailed!AY39/$AM$3</f>
+        <v>-7.7933684421795935E-2</v>
+      </c>
+      <c r="AA39" s="21">
+        <f>lc_detailed!AZ39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB39" s="21">
+        <f>lc_detailed!BA39/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC39" s="21">
+        <f>lc_detailed!BB39/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD39" s="21">
+        <f>lc_detailed!BC39/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE39" s="21">
+        <f>lc_detailed!BK39/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF39" s="21">
+        <f>lc_detailed!BL39/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG39" s="21">
+        <f>lc_detailed!BJ39</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH39" s="21">
+        <f>lc_detailed!AR39</f>
+        <v>1251.7308592440957</v>
+      </c>
+      <c r="AI39" s="21">
+        <f t="shared" si="2"/>
+        <v>27.450238141317886</v>
+      </c>
+      <c r="AJ39" s="21">
+        <f t="shared" si="3"/>
+        <v>27.450238141317886</v>
+      </c>
+    </row>
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B40" t="str">
+        <f>lc_detailed!AM40</f>
+        <v>CEN_TSC+CC90:H2</v>
+      </c>
+      <c r="C40" t="str">
+        <f>lc_detailed!AN40</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D40" s="21">
+        <f>lc_detailed!AU40/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="21">
+        <f>lc_detailed!AV40/$AM$3</f>
+        <v>-0.41514095054329514</v>
+      </c>
+      <c r="F40" s="21">
+        <f>lc_detailed!AW40/$AM$3</f>
+        <v>8.3482384672215804E-2</v>
+      </c>
+      <c r="G40" s="21">
+        <f>lc_detailed!AX40/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H40" s="21">
+        <f>lc_detailed!AY40/$AM$3</f>
+        <v>-7.7933684421795935E-2</v>
+      </c>
+      <c r="I40" s="21">
+        <f>lc_detailed!AZ40/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="21">
+        <f>lc_detailed!BA40/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K40" s="21">
+        <f>lc_detailed!BB40/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L40" s="21">
+        <f>lc_detailed!BC40/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M40" s="21">
+        <f>lc_detailed!BE40/$AM$3</f>
+        <v>-1.6211341286887113</v>
+      </c>
+      <c r="N40" s="21">
+        <f>lc_detailed!BF40/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O40" s="21">
+        <f>lc_detailed!BD40</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P40" s="21">
+        <f>lc_detailed!AO40</f>
+        <v>838.15148636495962</v>
+      </c>
+      <c r="Q40" s="21">
+        <f t="shared" si="0"/>
+        <v>18.380515051863149</v>
+      </c>
+      <c r="R40" s="21">
+        <f t="shared" si="1"/>
+        <v>18.380515051863146</v>
+      </c>
+      <c r="T40" t="str">
+        <f>lc_detailed!AM40</f>
+        <v>CEN_TSC+CC90:H2</v>
+      </c>
+      <c r="U40" t="str">
+        <f>lc_detailed!AN40</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V40" s="21">
+        <f>lc_detailed!AU40/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W40" s="21">
+        <f>lc_detailed!AV40/$AM$3</f>
+        <v>-0.41514095054329514</v>
+      </c>
+      <c r="X40" s="21">
+        <f>lc_detailed!AW40/$AM$3</f>
+        <v>8.3482384672215804E-2</v>
+      </c>
+      <c r="Y40" s="21">
+        <f>lc_detailed!AX40/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z40" s="21">
+        <f>lc_detailed!AY40/$AM$3</f>
+        <v>-7.7933684421795935E-2</v>
+      </c>
+      <c r="AA40" s="21">
+        <f>lc_detailed!AZ40/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB40" s="21">
+        <f>lc_detailed!BA40/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC40" s="21">
+        <f>lc_detailed!BB40/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD40" s="21">
+        <f>lc_detailed!BC40/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE40" s="21">
+        <f>lc_detailed!BK40/$AM$3</f>
+        <v>-1.6211341286887113</v>
+      </c>
+      <c r="AF40" s="21">
+        <f>lc_detailed!BL40/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG40" s="21">
+        <f>lc_detailed!BJ40</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH40" s="21">
+        <f>lc_detailed!AR40</f>
+        <v>1212.8367414650552</v>
+      </c>
+      <c r="AI40" s="21">
+        <f t="shared" si="2"/>
+        <v>26.597296961952964</v>
+      </c>
+      <c r="AJ40" s="21">
+        <f t="shared" si="3"/>
+        <v>26.59729696195296</v>
+      </c>
+    </row>
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B41" t="str">
+        <f>lc_detailed!AM41</f>
+        <v>CEN_TSC+H2in</v>
+      </c>
+      <c r="C41" t="str">
+        <f>lc_detailed!AN41</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D41" s="21">
+        <f>lc_detailed!AU41/$AM$3</f>
+        <v>5.7826274303884241E-2</v>
+      </c>
+      <c r="E41" s="21">
+        <f>lc_detailed!AV41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="21">
+        <f>lc_detailed!AW41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="21">
+        <f>lc_detailed!AX41/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H41" s="21">
+        <f>lc_detailed!AY41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="21">
+        <f>lc_detailed!AZ41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="21">
+        <f>lc_detailed!BA41/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K41" s="21">
+        <f>lc_detailed!BB41/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L41" s="21">
+        <f>lc_detailed!BC41/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M41" s="21">
+        <f>lc_detailed!BE41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="21">
+        <f>lc_detailed!BF41/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O41" s="21">
+        <f>lc_detailed!BD41</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P41" s="21">
+        <f>lc_detailed!AO41</f>
+        <v>857.25810316192656</v>
+      </c>
+      <c r="Q41" s="21">
+        <f t="shared" si="0"/>
+        <v>18.799519806182598</v>
+      </c>
+      <c r="R41" s="21">
+        <f t="shared" si="1"/>
+        <v>18.799519806182602</v>
+      </c>
+      <c r="T41" t="str">
+        <f>lc_detailed!AM41</f>
+        <v>CEN_TSC+H2in</v>
+      </c>
+      <c r="U41" t="str">
+        <f>lc_detailed!AN41</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V41" s="21">
+        <f>lc_detailed!AU41/$AM$3</f>
+        <v>5.7826274303884241E-2</v>
+      </c>
+      <c r="W41" s="21">
+        <f>lc_detailed!AV41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X41" s="21">
+        <f>lc_detailed!AW41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="21">
+        <f>lc_detailed!AX41/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z41" s="21">
+        <f>lc_detailed!AY41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA41" s="21">
+        <f>lc_detailed!AZ41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB41" s="21">
+        <f>lc_detailed!BA41/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC41" s="21">
+        <f>lc_detailed!BB41/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD41" s="21">
+        <f>lc_detailed!BC41/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE41" s="21">
+        <f>lc_detailed!BK41/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF41" s="21">
+        <f>lc_detailed!BL41/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG41" s="21">
+        <f>lc_detailed!BJ41</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH41" s="21">
+        <f>lc_detailed!AR41</f>
+        <v>1231.9433582632039</v>
+      </c>
+      <c r="AI41" s="21">
+        <f t="shared" si="2"/>
+        <v>27.016301716298329</v>
+      </c>
+      <c r="AJ41" s="21">
+        <f t="shared" si="3"/>
+        <v>27.016301716298333</v>
+      </c>
+    </row>
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B42" t="str">
+        <f>lc_detailed!AM42</f>
+        <v>CEN_TSC+H2in:CH4</v>
+      </c>
+      <c r="C42" t="str">
+        <f>lc_detailed!AN42</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D42" s="21">
+        <f>lc_detailed!AU42/$AM$3</f>
+        <v>0.3573146764212019</v>
+      </c>
+      <c r="E42" s="21">
+        <f>lc_detailed!AV42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="21">
+        <f>lc_detailed!AW42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="21">
+        <f>lc_detailed!AX42/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H42" s="21">
+        <f>lc_detailed!AY42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="21">
+        <f>lc_detailed!AZ42/$AM$3</f>
+        <v>6.9840858663496E-2</v>
+      </c>
+      <c r="J42" s="21">
+        <f>lc_detailed!BA42/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K42" s="21">
+        <f>lc_detailed!BB42/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L42" s="21">
+        <f>lc_detailed!BC42/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M42" s="21">
+        <f>lc_detailed!BE42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="21">
+        <f>lc_detailed!BF42/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O42" s="21">
+        <f>lc_detailed!BD42</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P42" s="21">
+        <f>lc_detailed!AO42</f>
+        <v>874.09951746601757</v>
+      </c>
+      <c r="Q42" s="21">
+        <f t="shared" si="0"/>
+        <v>19.168849067237225</v>
+      </c>
+      <c r="R42" s="21">
+        <f t="shared" si="1"/>
+        <v>19.168849067237229</v>
+      </c>
+      <c r="T42" t="str">
+        <f>lc_detailed!AM42</f>
+        <v>CEN_TSC+H2in:CH4</v>
+      </c>
+      <c r="U42" t="str">
+        <f>lc_detailed!AN42</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V42" s="21">
+        <f>lc_detailed!AU42/$AM$3</f>
+        <v>0.3573146764212019</v>
+      </c>
+      <c r="W42" s="21">
+        <f>lc_detailed!AV42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="21">
+        <f>lc_detailed!AW42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="21">
+        <f>lc_detailed!AX42/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z42" s="21">
+        <f>lc_detailed!AY42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA42" s="21">
+        <f>lc_detailed!AZ42/$AM$3</f>
+        <v>6.9840858663496E-2</v>
+      </c>
+      <c r="AB42" s="21">
+        <f>lc_detailed!BA42/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC42" s="21">
+        <f>lc_detailed!BB42/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD42" s="21">
+        <f>lc_detailed!BC42/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE42" s="21">
+        <f>lc_detailed!BK42/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF42" s="21">
+        <f>lc_detailed!BL42/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG42" s="21">
+        <f>lc_detailed!BJ42</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH42" s="21">
+        <f>lc_detailed!AR42</f>
+        <v>1248.784772554809</v>
+      </c>
+      <c r="AI42" s="21">
+        <f t="shared" si="2"/>
+        <v>27.385630977079146</v>
+      </c>
+      <c r="AJ42" s="21">
+        <f t="shared" si="3"/>
+        <v>27.385630977079149</v>
+      </c>
+    </row>
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B43" t="str">
+        <f>lc_detailed!AM43</f>
+        <v>SE_TSC+CC90</v>
+      </c>
+      <c r="C43" t="str">
+        <f>lc_detailed!AN43</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D43" s="21">
+        <f>lc_detailed!AU43/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="21">
+        <f>lc_detailed!AV43/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="21">
+        <f>lc_detailed!AW43/$AM$3</f>
+        <v>7.0202326938120979E-2</v>
+      </c>
+      <c r="G43" s="21">
+        <f>lc_detailed!AX43/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H43" s="21">
+        <f>lc_detailed!AY43/$AM$3</f>
+        <v>-1.3616107475968278E-2</v>
+      </c>
+      <c r="I43" s="21">
+        <f>lc_detailed!AZ43/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="21">
+        <f>lc_detailed!BA43/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K43" s="21">
+        <f>lc_detailed!BB43/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L43" s="21">
+        <f>lc_detailed!BC43/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M43" s="21">
+        <f>lc_detailed!BE43/$AM$3</f>
+        <v>-0.93405257145595821</v>
+      </c>
+      <c r="N43" s="21">
+        <f>lc_detailed!BF43/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O43" s="21">
+        <f>lc_detailed!BD43</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P43" s="21">
+        <f>lc_detailed!AO43</f>
+        <v>853.46206753114654</v>
+      </c>
+      <c r="Q43" s="21">
+        <f t="shared" si="0"/>
+        <v>18.716273410770757</v>
+      </c>
+      <c r="R43" s="21">
+        <f t="shared" si="1"/>
+        <v>18.716273410770754</v>
+      </c>
+      <c r="T43" t="str">
+        <f>lc_detailed!AM43</f>
+        <v>SE_TSC+CC90</v>
+      </c>
+      <c r="U43" t="str">
+        <f>lc_detailed!AN43</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V43" s="21">
+        <f>lc_detailed!AU43/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W43" s="21">
+        <f>lc_detailed!AV43/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X43" s="21">
+        <f>lc_detailed!AW43/$AM$3</f>
+        <v>7.0202326938120979E-2</v>
+      </c>
+      <c r="Y43" s="21">
+        <f>lc_detailed!AX43/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z43" s="21">
+        <f>lc_detailed!AY43/$AM$3</f>
+        <v>-1.3616107475968278E-2</v>
+      </c>
+      <c r="AA43" s="21">
+        <f>lc_detailed!AZ43/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB43" s="21">
+        <f>lc_detailed!BA43/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC43" s="21">
+        <f>lc_detailed!BB43/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD43" s="21">
+        <f>lc_detailed!BC43/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE43" s="21">
+        <f>lc_detailed!BK43/$AM$3</f>
+        <v>-0.93405257145595821</v>
+      </c>
+      <c r="AF43" s="21">
+        <f>lc_detailed!BL43/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG43" s="21">
+        <f>lc_detailed!BJ43</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH43" s="21">
+        <f>lc_detailed!AR43</f>
+        <v>1228.1473226333801</v>
+      </c>
+      <c r="AI43" s="21">
+        <f t="shared" si="2"/>
+        <v>26.933055320907457</v>
+      </c>
+      <c r="AJ43" s="21">
+        <f t="shared" si="3"/>
+        <v>26.933055320907453</v>
+      </c>
+    </row>
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B44" t="str">
+        <f>lc_detailed!AM44</f>
+        <v>SE_TSC:H2</v>
+      </c>
+      <c r="C44" t="str">
+        <f>lc_detailed!AN44</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D44" s="21">
+        <f>lc_detailed!AU44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="21">
+        <f>lc_detailed!AV44/$AM$3</f>
+        <v>-0.41197926741210172</v>
+      </c>
+      <c r="F44" s="21">
+        <f>lc_detailed!AW44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="21">
+        <f>lc_detailed!AX44/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H44" s="21">
+        <f>lc_detailed!AY44/$AM$3</f>
+        <v>-7.9070848071502525E-2</v>
+      </c>
+      <c r="I44" s="21">
+        <f>lc_detailed!AZ44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="21">
+        <f>lc_detailed!BA44/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K44" s="21">
+        <f>lc_detailed!BB44/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L44" s="21">
+        <f>lc_detailed!BC44/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M44" s="21">
+        <f>lc_detailed!BE44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="21">
+        <f>lc_detailed!BF44/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O44" s="21">
+        <f>lc_detailed!BD44</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P44" s="21">
+        <f>lc_detailed!AO44</f>
+        <v>877.13792221730364</v>
+      </c>
+      <c r="Q44" s="21">
+        <f t="shared" si="0"/>
+        <v>19.235480750379466</v>
+      </c>
+      <c r="R44" s="21">
+        <f t="shared" si="1"/>
+        <v>19.235480750379466</v>
+      </c>
+      <c r="T44" t="str">
+        <f>lc_detailed!AM44</f>
+        <v>SE_TSC:H2</v>
+      </c>
+      <c r="U44" t="str">
+        <f>lc_detailed!AN44</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V44" s="21">
+        <f>lc_detailed!AU44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W44" s="21">
+        <f>lc_detailed!AV44/$AM$3</f>
+        <v>-0.41197926741210172</v>
+      </c>
+      <c r="X44" s="21">
+        <f>lc_detailed!AW44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="21">
+        <f>lc_detailed!AX44/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z44" s="21">
+        <f>lc_detailed!AY44/$AM$3</f>
+        <v>-7.9070848071502525E-2</v>
+      </c>
+      <c r="AA44" s="21">
+        <f>lc_detailed!AZ44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB44" s="21">
+        <f>lc_detailed!BA44/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC44" s="21">
+        <f>lc_detailed!BB44/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD44" s="21">
+        <f>lc_detailed!BC44/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE44" s="21">
+        <f>lc_detailed!BK44/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF44" s="21">
+        <f>lc_detailed!BL44/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG44" s="21">
+        <f>lc_detailed!BJ44</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH44" s="21">
+        <f>lc_detailed!AR44</f>
+        <v>1251.8231773324515</v>
+      </c>
+      <c r="AI44" s="21">
+        <f t="shared" si="2"/>
+        <v>27.452262660799374</v>
+      </c>
+      <c r="AJ44" s="21">
+        <f t="shared" si="3"/>
+        <v>27.452262660799374</v>
+      </c>
+    </row>
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B45" t="str">
+        <f>lc_detailed!AM45</f>
+        <v>SE_TSC+CC90:H2</v>
+      </c>
+      <c r="C45" t="str">
+        <f>lc_detailed!AN45</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D45" s="21">
+        <f>lc_detailed!AU45/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="21">
+        <f>lc_detailed!AV45/$AM$3</f>
+        <v>-0.41197926741210172</v>
+      </c>
+      <c r="F45" s="21">
+        <f>lc_detailed!AW45/$AM$3</f>
+        <v>8.1847002378992201E-2</v>
+      </c>
+      <c r="G45" s="21">
+        <f>lc_detailed!AX45/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H45" s="21">
+        <f>lc_detailed!AY45/$AM$3</f>
+        <v>-7.9070848071502525E-2</v>
+      </c>
+      <c r="I45" s="21">
+        <f>lc_detailed!AZ45/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="21">
+        <f>lc_detailed!BA45/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K45" s="21">
+        <f>lc_detailed!BB45/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L45" s="21">
+        <f>lc_detailed!BC45/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M45" s="21">
+        <f>lc_detailed!BE45/$AM$3</f>
+        <v>-1.6230939201976322</v>
+      </c>
+      <c r="N45" s="21">
+        <f>lc_detailed!BF45/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O45" s="21">
+        <f>lc_detailed!BD45</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P45" s="21">
+        <f>lc_detailed!AO45</f>
+        <v>838.07986452793762</v>
+      </c>
+      <c r="Q45" s="21">
+        <f t="shared" si="0"/>
+        <v>18.37894439754249</v>
+      </c>
+      <c r="R45" s="21">
+        <f t="shared" si="1"/>
+        <v>18.378944397542487</v>
+      </c>
+      <c r="T45" t="str">
+        <f>lc_detailed!AM45</f>
+        <v>SE_TSC+CC90:H2</v>
+      </c>
+      <c r="U45" t="str">
+        <f>lc_detailed!AN45</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V45" s="21">
+        <f>lc_detailed!AU45/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W45" s="21">
+        <f>lc_detailed!AV45/$AM$3</f>
+        <v>-0.41197926741210172</v>
+      </c>
+      <c r="X45" s="21">
+        <f>lc_detailed!AW45/$AM$3</f>
+        <v>8.1847002378992201E-2</v>
+      </c>
+      <c r="Y45" s="21">
+        <f>lc_detailed!AX45/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z45" s="21">
+        <f>lc_detailed!AY45/$AM$3</f>
+        <v>-7.9070848071502525E-2</v>
+      </c>
+      <c r="AA45" s="21">
+        <f>lc_detailed!AZ45/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB45" s="21">
+        <f>lc_detailed!BA45/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC45" s="21">
+        <f>lc_detailed!BB45/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD45" s="21">
+        <f>lc_detailed!BC45/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE45" s="21">
+        <f>lc_detailed!BK45/$AM$3</f>
+        <v>-1.6230939201976322</v>
+      </c>
+      <c r="AF45" s="21">
+        <f>lc_detailed!BL45/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG45" s="21">
+        <f>lc_detailed!BJ45</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH45" s="21">
+        <f>lc_detailed!AR45</f>
+        <v>1212.7651196280331</v>
+      </c>
+      <c r="AI45" s="21">
+        <f t="shared" si="2"/>
+        <v>26.595726307632304</v>
+      </c>
+      <c r="AJ45" s="21">
+        <f t="shared" si="3"/>
+        <v>26.595726307632301</v>
+      </c>
+    </row>
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B46" t="str">
+        <f>lc_detailed!AM46</f>
+        <v>SE_TSC+H2in</v>
+      </c>
+      <c r="C46" t="str">
+        <f>lc_detailed!AN46</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D46" s="21">
+        <f>lc_detailed!AU46/$AM$3</f>
+        <v>5.7385873626073267E-2</v>
+      </c>
+      <c r="E46" s="21">
+        <f>lc_detailed!AV46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="21">
+        <f>lc_detailed!AW46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="21">
+        <f>lc_detailed!AX46/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H46" s="21">
+        <f>lc_detailed!AY46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="21">
+        <f>lc_detailed!AZ46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="21">
+        <f>lc_detailed!BA46/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K46" s="21">
+        <f>lc_detailed!BB46/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L46" s="21">
+        <f>lc_detailed!BC46/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M46" s="21">
+        <f>lc_detailed!BE46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="21">
+        <f>lc_detailed!BF46/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O46" s="21">
+        <f>lc_detailed!BD46</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P46" s="21">
+        <f>lc_detailed!AO46</f>
+        <v>857.23802089101855</v>
+      </c>
+      <c r="Q46" s="21">
+        <f t="shared" si="0"/>
+        <v>18.799079405504791</v>
+      </c>
+      <c r="R46" s="21">
+        <f t="shared" si="1"/>
+        <v>18.799079405504791</v>
+      </c>
+      <c r="T46" t="str">
+        <f>lc_detailed!AM46</f>
+        <v>SE_TSC+H2in</v>
+      </c>
+      <c r="U46" t="str">
+        <f>lc_detailed!AN46</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V46" s="21">
+        <f>lc_detailed!AU46/$AM$3</f>
+        <v>5.7385873626073267E-2</v>
+      </c>
+      <c r="W46" s="21">
+        <f>lc_detailed!AV46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="21">
+        <f>lc_detailed!AW46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="21">
+        <f>lc_detailed!AX46/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z46" s="21">
+        <f>lc_detailed!AY46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="21">
+        <f>lc_detailed!AZ46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB46" s="21">
+        <f>lc_detailed!BA46/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC46" s="21">
+        <f>lc_detailed!BB46/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD46" s="21">
+        <f>lc_detailed!BC46/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE46" s="21">
+        <f>lc_detailed!BK46/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF46" s="21">
+        <f>lc_detailed!BL46/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG46" s="21">
+        <f>lc_detailed!BJ46</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH46" s="21">
+        <f>lc_detailed!AR46</f>
+        <v>1231.9232759922959</v>
+      </c>
+      <c r="AI46" s="21">
+        <f t="shared" si="2"/>
+        <v>27.015861315620523</v>
+      </c>
+      <c r="AJ46" s="21">
+        <f t="shared" si="3"/>
+        <v>27.015861315620523</v>
+      </c>
+    </row>
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B47" t="str">
+        <f>lc_detailed!AM47</f>
+        <v>SE_TSC+H2in:CH4</v>
+      </c>
+      <c r="C47" t="str">
+        <f>lc_detailed!AN47</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D47" s="21">
+        <f>lc_detailed!AU47/$AM$3</f>
+        <v>0.35459339396643497</v>
+      </c>
+      <c r="E47" s="21">
+        <f>lc_detailed!AV47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="21">
+        <f>lc_detailed!AW47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="21">
+        <f>lc_detailed!AX47/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H47" s="21">
+        <f>lc_detailed!AY47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="21">
+        <f>lc_detailed!AZ47/$AM$3</f>
+        <v>7.0859936438730925E-2</v>
+      </c>
+      <c r="J47" s="21">
+        <f>lc_detailed!BA47/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K47" s="21">
+        <f>lc_detailed!BB47/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L47" s="21">
+        <f>lc_detailed!BC47/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M47" s="21">
+        <f>lc_detailed!BE47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="21">
+        <f>lc_detailed!BF47/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O47" s="21">
+        <f>lc_detailed!BD47</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P47" s="21">
+        <f>lc_detailed!AO47</f>
+        <v>874.02189693263097</v>
+      </c>
+      <c r="Q47" s="21">
+        <f t="shared" si="0"/>
+        <v>19.167146862557697</v>
+      </c>
+      <c r="R47" s="21">
+        <f t="shared" si="1"/>
+        <v>19.167146862557697</v>
+      </c>
+      <c r="T47" t="str">
+        <f>lc_detailed!AM47</f>
+        <v>SE_TSC+H2in:CH4</v>
+      </c>
+      <c r="U47" t="str">
+        <f>lc_detailed!AN47</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V47" s="21">
+        <f>lc_detailed!AU47/$AM$3</f>
+        <v>0.35459339396643497</v>
+      </c>
+      <c r="W47" s="21">
+        <f>lc_detailed!AV47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X47" s="21">
+        <f>lc_detailed!AW47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="21">
+        <f>lc_detailed!AX47/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z47" s="21">
+        <f>lc_detailed!AY47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA47" s="21">
+        <f>lc_detailed!AZ47/$AM$3</f>
+        <v>7.0859936438730925E-2</v>
+      </c>
+      <c r="AB47" s="21">
+        <f>lc_detailed!BA47/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC47" s="21">
+        <f>lc_detailed!BB47/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD47" s="21">
+        <f>lc_detailed!BC47/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE47" s="21">
+        <f>lc_detailed!BK47/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF47" s="21">
+        <f>lc_detailed!BL47/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG47" s="21">
+        <f>lc_detailed!BJ47</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH47" s="21">
+        <f>lc_detailed!AR47</f>
+        <v>1248.7071520214224</v>
+      </c>
+      <c r="AI47" s="21">
+        <f t="shared" si="2"/>
+        <v>27.383928772399614</v>
+      </c>
+      <c r="AJ47" s="21">
+        <f t="shared" si="3"/>
+        <v>27.383928772399617</v>
+      </c>
+    </row>
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B48" t="str">
+        <f>lc_detailed!AM48</f>
+        <v>MIDAT_TSC+CC90</v>
+      </c>
+      <c r="C48" t="str">
+        <f>lc_detailed!AN48</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D48" s="21">
+        <f>lc_detailed!AU48/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="21">
+        <f>lc_detailed!AV48/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="21">
+        <f>lc_detailed!AW48/$AM$3</f>
+        <v>7.2167177752049907E-2</v>
+      </c>
+      <c r="G48" s="21">
+        <f>lc_detailed!AX48/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H48" s="21">
+        <f>lc_detailed!AY48/$AM$3</f>
+        <v>-8.7210762247168436E-3</v>
+      </c>
+      <c r="I48" s="21">
+        <f>lc_detailed!AZ48/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="21">
+        <f>lc_detailed!BA48/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K48" s="21">
+        <f>lc_detailed!BB48/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L48" s="21">
+        <f>lc_detailed!BC48/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M48" s="21">
+        <f>lc_detailed!BE48/$AM$3</f>
+        <v>-0.83882543846807256</v>
+      </c>
+      <c r="N48" s="21">
+        <f>lc_detailed!BF48/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O48" s="21">
+        <f>lc_detailed!BD48</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P48" s="21">
+        <f>lc_detailed!AO48</f>
+        <v>858.11723541756635</v>
+      </c>
+      <c r="Q48" s="21">
+        <f t="shared" si="0"/>
+        <v>18.818360425823823</v>
+      </c>
+      <c r="R48" s="21">
+        <f t="shared" si="1"/>
+        <v>18.818360425823819</v>
+      </c>
+      <c r="T48" t="str">
+        <f>lc_detailed!AM48</f>
+        <v>MIDAT_TSC+CC90</v>
+      </c>
+      <c r="U48" t="str">
+        <f>lc_detailed!AN48</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V48" s="21">
+        <f>lc_detailed!AU48/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="21">
+        <f>lc_detailed!AV48/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X48" s="21">
+        <f>lc_detailed!AW48/$AM$3</f>
+        <v>7.2167177752049907E-2</v>
+      </c>
+      <c r="Y48" s="21">
+        <f>lc_detailed!AX48/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z48" s="21">
+        <f>lc_detailed!AY48/$AM$3</f>
+        <v>-8.7210762247168436E-3</v>
+      </c>
+      <c r="AA48" s="21">
+        <f>lc_detailed!AZ48/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB48" s="21">
+        <f>lc_detailed!BA48/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC48" s="21">
+        <f>lc_detailed!BB48/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD48" s="21">
+        <f>lc_detailed!BC48/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE48" s="21">
+        <f>lc_detailed!BK48/$AM$3</f>
+        <v>-0.83882543846807256</v>
+      </c>
+      <c r="AF48" s="21">
+        <f>lc_detailed!BL48/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG48" s="21">
+        <f>lc_detailed!BJ48</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH48" s="21">
+        <f>lc_detailed!AR48</f>
+        <v>1232.8024905197999</v>
+      </c>
+      <c r="AI48" s="21">
+        <f t="shared" si="2"/>
+        <v>27.035142335960522</v>
+      </c>
+      <c r="AJ48" s="21">
+        <f t="shared" si="3"/>
+        <v>27.035142335960519</v>
+      </c>
+    </row>
+    <row r="49" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B49" t="str">
+        <f>lc_detailed!AM49</f>
+        <v>MIDAT_TSC:H2</v>
+      </c>
+      <c r="C49" t="str">
+        <f>lc_detailed!AN49</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D49" s="21">
+        <f>lc_detailed!AU49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="21">
+        <f>lc_detailed!AV49/$AM$3</f>
+        <v>-0.5311353695838219</v>
+      </c>
+      <c r="F49" s="21">
+        <f>lc_detailed!AW49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="21">
+        <f>lc_detailed!AX49/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H49" s="21">
+        <f>lc_detailed!AY49/$AM$3</f>
+        <v>-5.0644642340085554E-2</v>
+      </c>
+      <c r="I49" s="21">
+        <f>lc_detailed!AZ49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="21">
+        <f>lc_detailed!BA49/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K49" s="21">
+        <f>lc_detailed!BB49/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L49" s="21">
+        <f>lc_detailed!BC49/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M49" s="21">
+        <f>lc_detailed!BE49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="21">
+        <f>lc_detailed!BF49/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O49" s="21">
+        <f>lc_detailed!BD49</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P49" s="21">
+        <f>lc_detailed!AO49</f>
+        <v>873.00063893962579</v>
+      </c>
+      <c r="Q49" s="21">
+        <f t="shared" si="0"/>
+        <v>19.144750853939161</v>
+      </c>
+      <c r="R49" s="21">
+        <f t="shared" si="1"/>
+        <v>19.144750853939161</v>
+      </c>
+      <c r="T49" t="str">
+        <f>lc_detailed!AM49</f>
+        <v>MIDAT_TSC:H2</v>
+      </c>
+      <c r="U49" t="str">
+        <f>lc_detailed!AN49</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V49" s="21">
+        <f>lc_detailed!AU49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="21">
+        <f>lc_detailed!AV49/$AM$3</f>
+        <v>-0.5311353695838219</v>
+      </c>
+      <c r="X49" s="21">
+        <f>lc_detailed!AW49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="21">
+        <f>lc_detailed!AX49/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z49" s="21">
+        <f>lc_detailed!AY49/$AM$3</f>
+        <v>-5.0644642340085554E-2</v>
+      </c>
+      <c r="AA49" s="21">
+        <f>lc_detailed!AZ49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB49" s="21">
+        <f>lc_detailed!BA49/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC49" s="21">
+        <f>lc_detailed!BB49/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD49" s="21">
+        <f>lc_detailed!BC49/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE49" s="21">
+        <f>lc_detailed!BK49/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF49" s="21">
+        <f>lc_detailed!BL49/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG49" s="21">
+        <f>lc_detailed!BJ49</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH49" s="21">
+        <f>lc_detailed!AR49</f>
+        <v>1247.6858940547736</v>
+      </c>
+      <c r="AI49" s="21">
+        <f t="shared" si="2"/>
+        <v>27.361532764359069</v>
+      </c>
+      <c r="AJ49" s="21">
+        <f t="shared" si="3"/>
+        <v>27.361532764359069</v>
+      </c>
+    </row>
+    <row r="50" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B50" t="str">
+        <f>lc_detailed!AM50</f>
+        <v>MIDAT_TSC+CC90:H2</v>
+      </c>
+      <c r="C50" t="str">
+        <f>lc_detailed!AN50</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D50" s="21">
+        <f>lc_detailed!AU50/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="21">
+        <f>lc_detailed!AV50/$AM$3</f>
+        <v>-0.5311353695838219</v>
+      </c>
+      <c r="F50" s="21">
+        <f>lc_detailed!AW50/$AM$3</f>
+        <v>8.4137769028134135E-2</v>
+      </c>
+      <c r="G50" s="21">
+        <f>lc_detailed!AX50/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H50" s="21">
+        <f>lc_detailed!AY50/$AM$3</f>
+        <v>-5.0644642340085554E-2</v>
+      </c>
+      <c r="I50" s="21">
+        <f>lc_detailed!AZ50/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="21">
+        <f>lc_detailed!BA50/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K50" s="21">
+        <f>lc_detailed!BB50/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L50" s="21">
+        <f>lc_detailed!BC50/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M50" s="21">
+        <f>lc_detailed!BE50/$AM$3</f>
+        <v>-1.4576186725361822</v>
+      </c>
+      <c r="N50" s="21">
+        <f>lc_detailed!BF50/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O50" s="21">
+        <f>lc_detailed!BD50</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P50" s="21">
+        <f>lc_detailed!AO50</f>
+        <v>841.59271150282279</v>
+      </c>
+      <c r="Q50" s="21">
+        <f t="shared" si="0"/>
+        <v>18.455980515412779</v>
+      </c>
+      <c r="R50" s="21">
+        <f t="shared" si="1"/>
+        <v>18.455980515412776</v>
+      </c>
+      <c r="T50" t="str">
+        <f>lc_detailed!AM50</f>
+        <v>MIDAT_TSC+CC90:H2</v>
+      </c>
+      <c r="U50" t="str">
+        <f>lc_detailed!AN50</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V50" s="21">
+        <f>lc_detailed!AU50/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W50" s="21">
+        <f>lc_detailed!AV50/$AM$3</f>
+        <v>-0.5311353695838219</v>
+      </c>
+      <c r="X50" s="21">
+        <f>lc_detailed!AW50/$AM$3</f>
+        <v>8.4137769028134135E-2</v>
+      </c>
+      <c r="Y50" s="21">
+        <f>lc_detailed!AX50/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z50" s="21">
+        <f>lc_detailed!AY50/$AM$3</f>
+        <v>-5.0644642340085554E-2</v>
+      </c>
+      <c r="AA50" s="21">
+        <f>lc_detailed!AZ50/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB50" s="21">
+        <f>lc_detailed!BA50/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC50" s="21">
+        <f>lc_detailed!BB50/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD50" s="21">
+        <f>lc_detailed!BC50/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE50" s="21">
+        <f>lc_detailed!BK50/$AM$3</f>
+        <v>-1.4576186725361822</v>
+      </c>
+      <c r="AF50" s="21">
+        <f>lc_detailed!BL50/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG50" s="21">
+        <f>lc_detailed!BJ50</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH50" s="21">
+        <f>lc_detailed!AR50</f>
+        <v>1216.2779666029182</v>
+      </c>
+      <c r="AI50" s="21">
+        <f t="shared" si="2"/>
+        <v>26.672762425502594</v>
+      </c>
+      <c r="AJ50" s="21">
+        <f t="shared" si="3"/>
+        <v>26.67276242550259</v>
+      </c>
+    </row>
+    <row r="51" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B51" t="str">
+        <f>lc_detailed!AM51</f>
+        <v>MIDAT_TSC+H2in</v>
+      </c>
+      <c r="C51" t="str">
+        <f>lc_detailed!AN51</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D51" s="21">
+        <f>lc_detailed!AU51/$AM$3</f>
+        <v>7.3983497734574591E-2</v>
+      </c>
+      <c r="E51" s="21">
+        <f>lc_detailed!AV51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="21">
+        <f>lc_detailed!AW51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="21">
+        <f>lc_detailed!AX51/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H51" s="21">
+        <f>lc_detailed!AY51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="21">
+        <f>lc_detailed!AZ51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="21">
+        <f>lc_detailed!BA51/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K51" s="21">
+        <f>lc_detailed!BB51/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L51" s="21">
+        <f>lc_detailed!BC51/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M51" s="21">
+        <f>lc_detailed!BE51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="21">
+        <f>lc_detailed!BF51/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O51" s="21">
+        <f>lc_detailed!BD51</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P51" s="21">
+        <f>lc_detailed!AO51</f>
+        <v>857.99487255036615</v>
+      </c>
+      <c r="Q51" s="21">
+        <f t="shared" si="0"/>
+        <v>18.815677029613294</v>
+      </c>
+      <c r="R51" s="21">
+        <f t="shared" si="1"/>
+        <v>18.815677029613294</v>
+      </c>
+      <c r="T51" t="str">
+        <f>lc_detailed!AM51</f>
+        <v>MIDAT_TSC+H2in</v>
+      </c>
+      <c r="U51" t="str">
+        <f>lc_detailed!AN51</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V51" s="21">
+        <f>lc_detailed!AU51/$AM$3</f>
+        <v>7.3983497734574591E-2</v>
+      </c>
+      <c r="W51" s="21">
+        <f>lc_detailed!AV51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X51" s="21">
+        <f>lc_detailed!AW51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="21">
+        <f>lc_detailed!AX51/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z51" s="21">
+        <f>lc_detailed!AY51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="21">
+        <f>lc_detailed!AZ51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB51" s="21">
+        <f>lc_detailed!BA51/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC51" s="21">
+        <f>lc_detailed!BB51/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD51" s="21">
+        <f>lc_detailed!BC51/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE51" s="21">
+        <f>lc_detailed!BK51/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF51" s="21">
+        <f>lc_detailed!BL51/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG51" s="21">
+        <f>lc_detailed!BJ51</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH51" s="21">
+        <f>lc_detailed!AR51</f>
+        <v>1232.6801276516435</v>
+      </c>
+      <c r="AI51" s="21">
+        <f t="shared" si="2"/>
+        <v>27.032458939729022</v>
+      </c>
+      <c r="AJ51" s="21">
+        <f t="shared" si="3"/>
+        <v>27.032458939729025</v>
+      </c>
+    </row>
+    <row r="52" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B52" t="str">
+        <f>lc_detailed!AM52</f>
+        <v>MIDAT_TSC+H2in:CH4</v>
+      </c>
+      <c r="C52" t="str">
+        <f>lc_detailed!AN52</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D52" s="21">
+        <f>lc_detailed!AU52/$AM$3</f>
+        <v>0.4571518720818325</v>
+      </c>
+      <c r="E52" s="21">
+        <f>lc_detailed!AV52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="21">
+        <f>lc_detailed!AW52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="21">
+        <f>lc_detailed!AX52/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H52" s="21">
+        <f>lc_detailed!AY52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="21">
+        <f>lc_detailed!AZ52/$AM$3</f>
+        <v>4.5385577930510373E-2</v>
+      </c>
+      <c r="J52" s="21">
+        <f>lc_detailed!BA52/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K52" s="21">
+        <f>lc_detailed!BB52/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L52" s="21">
+        <f>lc_detailed!BC52/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M52" s="21">
+        <f>lc_detailed!BE52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="21">
+        <f>lc_detailed!BF52/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O52" s="21">
+        <f>lc_detailed!BD52</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P52" s="21">
+        <f>lc_detailed!AO52</f>
+        <v>877.53693278671824</v>
+      </c>
+      <c r="Q52" s="21">
+        <f t="shared" si="0"/>
+        <v>19.244230982164872</v>
+      </c>
+      <c r="R52" s="21">
+        <f t="shared" si="1"/>
+        <v>19.244230982164872</v>
+      </c>
+      <c r="T52" t="str">
+        <f>lc_detailed!AM52</f>
+        <v>MIDAT_TSC+H2in:CH4</v>
+      </c>
+      <c r="U52" t="str">
+        <f>lc_detailed!AN52</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V52" s="21">
+        <f>lc_detailed!AU52/$AM$3</f>
+        <v>0.4571518720818325</v>
+      </c>
+      <c r="W52" s="21">
+        <f>lc_detailed!AV52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="21">
+        <f>lc_detailed!AW52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="21">
+        <f>lc_detailed!AX52/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z52" s="21">
+        <f>lc_detailed!AY52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA52" s="21">
+        <f>lc_detailed!AZ52/$AM$3</f>
+        <v>4.5385577930510373E-2</v>
+      </c>
+      <c r="AB52" s="21">
+        <f>lc_detailed!BA52/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC52" s="21">
+        <f>lc_detailed!BB52/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD52" s="21">
+        <f>lc_detailed!BC52/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE52" s="21">
+        <f>lc_detailed!BK52/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF52" s="21">
+        <f>lc_detailed!BL52/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG52" s="21">
+        <f>lc_detailed!BJ52</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH52" s="21">
+        <f>lc_detailed!AR52</f>
+        <v>1252.2221878755097</v>
+      </c>
+      <c r="AI52" s="21">
+        <f t="shared" si="2"/>
+        <v>27.461012892006792</v>
+      </c>
+      <c r="AJ52" s="21">
+        <f t="shared" si="3"/>
+        <v>27.461012892006792</v>
+      </c>
+    </row>
+    <row r="53" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B53" t="str">
+        <f>lc_detailed!AM53</f>
+        <v>NE_TSC+CC90</v>
+      </c>
+      <c r="C53" t="str">
+        <f>lc_detailed!AN53</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D53" s="21">
+        <f>lc_detailed!AU53/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="21">
+        <f>lc_detailed!AV53/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="21">
+        <f>lc_detailed!AW53/$AM$3</f>
+        <v>6.9766309784054834E-2</v>
+      </c>
+      <c r="G53" s="21">
+        <f>lc_detailed!AX53/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H53" s="21">
+        <f>lc_detailed!AY53/$AM$3</f>
+        <v>5.5208385176549898E-2</v>
+      </c>
+      <c r="I53" s="21">
+        <f>lc_detailed!AZ53/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="21">
+        <f>lc_detailed!BA53/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="K53" s="21">
+        <f>lc_detailed!BB53/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="L53" s="21">
+        <f>lc_detailed!BC53/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="M53" s="21">
+        <f>lc_detailed!BE53/$AM$3</f>
+        <v>-0.77832841723626556</v>
+      </c>
+      <c r="N53" s="21">
+        <f>lc_detailed!BF53/$AM$3</f>
+        <v>1.1051347859602165</v>
+      </c>
+      <c r="O53" s="21">
+        <f>lc_detailed!BD53</f>
+        <v>0.50437876887805144</v>
+      </c>
+      <c r="P53" s="21">
+        <f>lc_detailed!AO53</f>
+        <v>863.68160344629393</v>
+      </c>
+      <c r="Q53" s="21">
+        <f t="shared" si="0"/>
+        <v>18.940386040488903</v>
+      </c>
+      <c r="R53" s="21">
+        <f t="shared" si="1"/>
+        <v>18.940386040488896</v>
+      </c>
+      <c r="T53" t="str">
+        <f>lc_detailed!AM53</f>
+        <v>NE_TSC+CC90</v>
+      </c>
+      <c r="U53" t="str">
+        <f>lc_detailed!AN53</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V53" s="21">
+        <f>lc_detailed!AU53/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="21">
+        <f>lc_detailed!AV53/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="21">
+        <f>lc_detailed!AW53/$AM$3</f>
+        <v>6.9766309784054834E-2</v>
+      </c>
+      <c r="Y53" s="21">
+        <f>lc_detailed!AX53/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z53" s="21">
+        <f>lc_detailed!AY53/$AM$3</f>
+        <v>5.5208385176549898E-2</v>
+      </c>
+      <c r="AA53" s="21">
+        <f>lc_detailed!AZ53/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB53" s="21">
+        <f>lc_detailed!BA53/$AM$3</f>
+        <v>5.5982890881479141</v>
+      </c>
+      <c r="AC53" s="21">
+        <f>lc_detailed!BB53/$AM$3</f>
+        <v>3.0641325531920858</v>
+      </c>
+      <c r="AD53" s="21">
+        <f>lc_detailed!BC53/$AM$3</f>
+        <v>0.74634069943059123</v>
+      </c>
+      <c r="AE53" s="21">
+        <f>lc_detailed!BK53/$AM$3</f>
+        <v>-0.77832841723626556</v>
+      </c>
+      <c r="AF53" s="21">
+        <f>lc_detailed!BL53/$AM$3</f>
+        <v>9.3219166960969169</v>
+      </c>
+      <c r="AG53" s="21">
+        <f>lc_detailed!BJ53</f>
+        <v>4.2544827350411296</v>
+      </c>
+      <c r="AH53" s="21">
+        <f>lc_detailed!AR53</f>
+        <v>1238.3668585485275</v>
+      </c>
+      <c r="AI53" s="21">
+        <f t="shared" si="2"/>
+        <v>27.157167950625603</v>
+      </c>
+      <c r="AJ53" s="21">
+        <f t="shared" si="3"/>
+        <v>27.157167950625595</v>
+      </c>
+    </row>
+    <row r="54" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B54" t="str">
+        <f>lc_detailed!AM54</f>
+        <v>NE_TSC:H2</v>
+      </c>
+      <c r="C54" t="str">
+        <f>lc_detailed!AN54</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D54" s="21">
+        <f>lc_detailed!AU54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="21">
+        <f>lc_detailed!AV54/$AM$3</f>
+        <v>-0.82828077146940482</v>
+      </c>
+      <c r="F54" s="21">
+        <f>lc_detailed!AW54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="21">
+        <f>lc_detailed!AX54/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H54" s="21">
+        <f>lc_detailed!AY54/$AM$3</f>
+        <v>0.32060365594738643</v>
+      </c>
+      <c r="I54" s="21">
+        <f>lc_detailed!AZ54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="21">
+        <f>lc_detailed!BA54/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K54" s="21">
+        <f>lc_detailed!BB54/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L54" s="21">
+        <f>lc_detailed!BC54/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M54" s="21">
+        <f>lc_detailed!BE54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="21">
+        <f>lc_detailed!BF54/$AM$3</f>
+        <v>1.9203817928465909</v>
+      </c>
+      <c r="O54" s="21">
+        <f>lc_detailed!BD54</f>
+        <v>0.8764540006857201</v>
+      </c>
+      <c r="P54" s="21">
+        <f>lc_detailed!AO54</f>
+        <v>876.3797310155519</v>
+      </c>
+      <c r="Q54" s="21">
+        <f t="shared" si="0"/>
+        <v>19.218853750341051</v>
+      </c>
+      <c r="R54" s="21">
+        <f t="shared" si="1"/>
+        <v>19.218853750341051</v>
+      </c>
+      <c r="T54" t="str">
+        <f>lc_detailed!AM54</f>
+        <v>NE_TSC:H2</v>
+      </c>
+      <c r="U54" t="str">
+        <f>lc_detailed!AN54</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V54" s="21">
+        <f>lc_detailed!AU54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W54" s="21">
+        <f>lc_detailed!AV54/$AM$3</f>
+        <v>-0.82828077146940482</v>
+      </c>
+      <c r="X54" s="21">
+        <f>lc_detailed!AW54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="21">
+        <f>lc_detailed!AX54/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z54" s="21">
+        <f>lc_detailed!AY54/$AM$3</f>
+        <v>0.32060365594738643</v>
+      </c>
+      <c r="AA54" s="21">
+        <f>lc_detailed!AZ54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB54" s="21">
+        <f>lc_detailed!BA54/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC54" s="21">
+        <f>lc_detailed!BB54/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD54" s="21">
+        <f>lc_detailed!BC54/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE54" s="21">
+        <f>lc_detailed!BK54/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF54" s="21">
+        <f>lc_detailed!BL54/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG54" s="21">
+        <f>lc_detailed!BJ54</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH54" s="21">
+        <f>lc_detailed!AR54</f>
+        <v>1251.0649861306997</v>
+      </c>
+      <c r="AI54" s="21">
+        <f t="shared" si="2"/>
+        <v>27.435635660760958</v>
+      </c>
+      <c r="AJ54" s="21">
+        <f t="shared" si="3"/>
+        <v>27.435635660760958</v>
+      </c>
+    </row>
+    <row r="55" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B55" t="str">
+        <f>lc_detailed!AM55</f>
+        <v>NE_TSC+CC90:H2</v>
+      </c>
+      <c r="C55" t="str">
+        <f>lc_detailed!AN55</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D55" s="21">
+        <f>lc_detailed!AU55/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="21">
+        <f>lc_detailed!AV55/$AM$3</f>
+        <v>-0.82828077146940482</v>
+      </c>
+      <c r="F55" s="21">
+        <f>lc_detailed!AW55/$AM$3</f>
+        <v>8.1338661721315875E-2</v>
+      </c>
+      <c r="G55" s="21">
+        <f>lc_detailed!AX55/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H55" s="21">
+        <f>lc_detailed!AY55/$AM$3</f>
+        <v>0.32060365594738643</v>
+      </c>
+      <c r="I55" s="21">
+        <f>lc_detailed!AZ55/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="21">
+        <f>lc_detailed!BA55/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="K55" s="21">
+        <f>lc_detailed!BB55/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="L55" s="21">
+        <f>lc_detailed!BC55/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="M55" s="21">
+        <f>lc_detailed!BE55/$AM$3</f>
+        <v>-1.3524935967619618</v>
+      </c>
+      <c r="N55" s="21">
+        <f>lc_detailed!BF55/$AM$3</f>
+        <v>1.9203817931766853</v>
+      </c>
+      <c r="O55" s="21">
+        <f>lc_detailed!BD55</f>
+        <v>0.87645400083637381</v>
+      </c>
+      <c r="P55" s="21">
+        <f>lc_detailed!AO55</f>
+        <v>849.63786774086236</v>
+      </c>
+      <c r="Q55" s="21">
+        <f t="shared" si="0"/>
+        <v>18.63240938028207</v>
+      </c>
+      <c r="R55" s="21">
+        <f t="shared" si="1"/>
+        <v>18.632409380282066</v>
+      </c>
+      <c r="T55" t="str">
+        <f>lc_detailed!AM55</f>
+        <v>NE_TSC+CC90:H2</v>
+      </c>
+      <c r="U55" t="str">
+        <f>lc_detailed!AN55</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V55" s="21">
+        <f>lc_detailed!AU55/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W55" s="21">
+        <f>lc_detailed!AV55/$AM$3</f>
+        <v>-0.82828077146940482</v>
+      </c>
+      <c r="X55" s="21">
+        <f>lc_detailed!AW55/$AM$3</f>
+        <v>8.1338661721315875E-2</v>
+      </c>
+      <c r="Y55" s="21">
+        <f>lc_detailed!AX55/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z55" s="21">
+        <f>lc_detailed!AY55/$AM$3</f>
+        <v>0.32060365594738643</v>
+      </c>
+      <c r="AA55" s="21">
+        <f>lc_detailed!AZ55/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB55" s="21">
+        <f>lc_detailed!BA55/$AM$3</f>
+        <v>5.5996407631099441</v>
+      </c>
+      <c r="AC55" s="21">
+        <f>lc_detailed!BB55/$AM$3</f>
+        <v>3.0648553418449445</v>
+      </c>
+      <c r="AD55" s="21">
+        <f>lc_detailed!BC55/$AM$3</f>
+        <v>0.74652089667940558</v>
+      </c>
+      <c r="AE55" s="21">
+        <f>lc_detailed!BK55/$AM$3</f>
+        <v>-1.3524935967619618</v>
+      </c>
+      <c r="AF55" s="21">
+        <f>lc_detailed!BL55/$AM$3</f>
+        <v>10.137163703266499</v>
+      </c>
+      <c r="AG55" s="21">
+        <f>lc_detailed!BJ55</f>
+        <v>4.6265579669780523</v>
+      </c>
+      <c r="AH55" s="21">
+        <f>lc_detailed!AR55</f>
+        <v>1224.3231228409577</v>
+      </c>
+      <c r="AI55" s="21">
+        <f t="shared" si="2"/>
+        <v>26.849191290371877</v>
+      </c>
+      <c r="AJ55" s="21">
+        <f t="shared" si="3"/>
+        <v>26.849191290371881</v>
+      </c>
+    </row>
+    <row r="56" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B56" t="str">
+        <f>lc_detailed!AM56</f>
+        <v>NE_TSC+H2in</v>
+      </c>
+      <c r="C56" t="str">
+        <f>lc_detailed!AN56</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D56" s="21">
+        <f>lc_detailed!AU56/$AM$3</f>
+        <v>0.11537380503884434</v>
+      </c>
+      <c r="E56" s="21">
+        <f>lc_detailed!AV56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="21">
+        <f>lc_detailed!AW56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="21">
+        <f>lc_detailed!AX56/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H56" s="21">
+        <f>lc_detailed!AY56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="21">
+        <f>lc_detailed!AZ56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="21">
+        <f>lc_detailed!BA56/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K56" s="21">
+        <f>lc_detailed!BB56/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L56" s="21">
+        <f>lc_detailed!BC56/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M56" s="21">
+        <f>lc_detailed!BE56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="21">
+        <f>lc_detailed!BF56/$AM$3</f>
+        <v>0.93554445886223792</v>
+      </c>
+      <c r="O56" s="21">
+        <f>lc_detailed!BD56</f>
+        <v>0.42697847211607459</v>
+      </c>
+      <c r="P56" s="21">
+        <f>lc_detailed!AO56</f>
+        <v>859.8822705634409</v>
+      </c>
+      <c r="Q56" s="21">
+        <f t="shared" si="0"/>
+        <v>18.857067336917563</v>
+      </c>
+      <c r="R56" s="21">
+        <f t="shared" si="1"/>
+        <v>18.857067336917563</v>
+      </c>
+      <c r="T56" t="str">
+        <f>lc_detailed!AM56</f>
+        <v>NE_TSC+H2in</v>
+      </c>
+      <c r="U56" t="str">
+        <f>lc_detailed!AN56</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V56" s="21">
+        <f>lc_detailed!AU56/$AM$3</f>
+        <v>0.11537380503884434</v>
+      </c>
+      <c r="W56" s="21">
+        <f>lc_detailed!AV56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X56" s="21">
+        <f>lc_detailed!AW56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y56" s="21">
+        <f>lc_detailed!AX56/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z56" s="21">
+        <f>lc_detailed!AY56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA56" s="21">
+        <f>lc_detailed!AZ56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AB56" s="21">
+        <f>lc_detailed!BA56/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC56" s="21">
+        <f>lc_detailed!BB56/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD56" s="21">
+        <f>lc_detailed!BC56/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE56" s="21">
+        <f>lc_detailed!BK56/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF56" s="21">
+        <f>lc_detailed!BL56/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG56" s="21">
+        <f>lc_detailed!BJ56</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH56" s="21">
+        <f>lc_detailed!AR56</f>
+        <v>1234.5675256647182</v>
+      </c>
+      <c r="AI56" s="21">
+        <f t="shared" si="2"/>
+        <v>27.073849247033294</v>
+      </c>
+      <c r="AJ56" s="21">
+        <f t="shared" si="3"/>
+        <v>27.073849247033294</v>
+      </c>
+    </row>
+    <row r="57" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B57" t="str">
+        <f>lc_detailed!AM57</f>
+        <v>NE_TSC+H2in:CH4</v>
+      </c>
+      <c r="C57" t="str">
+        <f>lc_detailed!AN57</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D57" s="21">
+        <f>lc_detailed!AU57/$AM$3</f>
+        <v>0.71290696679326626</v>
+      </c>
+      <c r="E57" s="21">
+        <f>lc_detailed!AV57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="21">
+        <f>lc_detailed!AW57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="21">
+        <f>lc_detailed!AX57/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H57" s="21">
+        <f>lc_detailed!AY57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="21">
+        <f>lc_detailed!AZ57/$AM$3</f>
+        <v>-0.28731138259593558</v>
+      </c>
+      <c r="J57" s="21">
+        <f>lc_detailed!BA57/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="K57" s="21">
+        <f>lc_detailed!BB57/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="L57" s="21">
+        <f>lc_detailed!BC57/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="M57" s="21">
+        <f>lc_detailed!BE57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="21">
+        <f>lc_detailed!BF57/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O57" s="21">
+        <f>lc_detailed!BD57</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P57" s="21">
+        <f>lc_detailed!AO57</f>
+        <v>874.02838370555367</v>
+      </c>
+      <c r="Q57" s="21">
+        <f t="shared" si="0"/>
+        <v>19.16728911634986</v>
+      </c>
+      <c r="R57" s="21">
+        <f t="shared" si="1"/>
+        <v>19.16728911634986</v>
+      </c>
+      <c r="T57" t="str">
+        <f>lc_detailed!AM57</f>
+        <v>NE_TSC+H2in:CH4</v>
+      </c>
+      <c r="U57" t="str">
+        <f>lc_detailed!AN57</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V57" s="21">
+        <f>lc_detailed!AU57/$AM$3</f>
+        <v>0.71290696679326626</v>
+      </c>
+      <c r="W57" s="21">
+        <f>lc_detailed!AV57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="X57" s="21">
+        <f>lc_detailed!AW57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="21">
+        <f>lc_detailed!AX57/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z57" s="21">
+        <f>lc_detailed!AY57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA57" s="21">
+        <f>lc_detailed!AZ57/$AM$3</f>
+        <v>-0.28731138259593558</v>
+      </c>
+      <c r="AB57" s="21">
+        <f>lc_detailed!BA57/$AM$3</f>
+        <v>5.1922874272807658</v>
+      </c>
+      <c r="AC57" s="21">
+        <f>lc_detailed!BB57/$AM$3</f>
+        <v>2.8418047707297904</v>
+      </c>
+      <c r="AD57" s="21">
+        <f>lc_detailed!BC57/$AM$3</f>
+        <v>0.69221423897216883</v>
+      </c>
+      <c r="AE57" s="21">
+        <f>lc_detailed!BK57/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF57" s="21">
+        <f>lc_detailed!BL57/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG57" s="21">
+        <f>lc_detailed!BJ57</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH57" s="21">
+        <f>lc_detailed!AR57</f>
+        <v>1248.7136387943451</v>
+      </c>
+      <c r="AI57" s="21">
+        <f t="shared" si="2"/>
+        <v>27.384071026191776</v>
+      </c>
+      <c r="AJ57" s="21">
+        <f t="shared" si="3"/>
+        <v>27.38407102619178</v>
+      </c>
+    </row>
+    <row r="58" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B58" t="str">
+        <f>lc_detailed!AM58</f>
+        <v>CA_ESC</v>
+      </c>
+      <c r="C58" t="str">
+        <f>lc_detailed!AN58</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D58" s="21">
+        <f>lc_detailed!AU58/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="21">
+        <f>lc_detailed!AV58/$AM$3</f>
+        <v>-0.30639510581400747</v>
+      </c>
+      <c r="F58" s="21">
+        <f>lc_detailed!AW58/$AM$3</f>
+        <v>1.5190713853820867</v>
+      </c>
+      <c r="G58" s="21">
+        <f>lc_detailed!AX58/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H58" s="21">
+        <f>lc_detailed!AY58/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="21">
+        <f>lc_detailed!AZ58/$AM$3</f>
+        <v>0.15299954696665649</v>
+      </c>
+      <c r="J58" s="21">
+        <f>lc_detailed!BA58/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K58" s="21">
+        <f>lc_detailed!BB58/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L58" s="21">
+        <f>lc_detailed!BC58/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M58" s="21">
+        <f>lc_detailed!BE58/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="21">
+        <f>lc_detailed!BF58/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O58" s="21">
+        <f>lc_detailed!BD58</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P58" s="21">
+        <f>lc_detailed!AO58</f>
+        <v>1046.1572430901124</v>
+      </c>
+      <c r="Q58" s="21">
+        <f t="shared" si="0"/>
+        <v>22.942044804607725</v>
+      </c>
+      <c r="R58" s="21">
+        <f t="shared" si="1"/>
+        <v>22.942044804607718</v>
+      </c>
+      <c r="T58" t="str">
+        <f>lc_detailed!AM58</f>
+        <v>CA_ESC</v>
+      </c>
+      <c r="U58" t="str">
+        <f>lc_detailed!AN58</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V58" s="21">
+        <f>lc_detailed!AU58/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W58" s="21">
+        <f>lc_detailed!AV58/$AM$3</f>
+        <v>-0.30639510581400747</v>
+      </c>
+      <c r="X58" s="21">
+        <f>lc_detailed!AW58/$AM$3</f>
+        <v>1.5190713853820867</v>
+      </c>
+      <c r="Y58" s="21">
+        <f>lc_detailed!AX58/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z58" s="21">
+        <f>lc_detailed!AY58/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA58" s="21">
+        <f>lc_detailed!AZ58/$AM$3</f>
+        <v>0.15299954696665649</v>
+      </c>
+      <c r="AB58" s="21">
+        <f>lc_detailed!BA58/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC58" s="21">
+        <f>lc_detailed!BB58/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD58" s="21">
+        <f>lc_detailed!BC58/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE58" s="21">
+        <f>lc_detailed!BK58/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF58" s="21">
+        <f>lc_detailed!BL58/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG58" s="21">
+        <f>lc_detailed!BJ58</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH58" s="21">
+        <f>lc_detailed!AR58</f>
+        <v>1420.842498178904</v>
+      </c>
+      <c r="AI58" s="21">
+        <f t="shared" si="2"/>
+        <v>31.158826714449646</v>
+      </c>
+      <c r="AJ58" s="21">
+        <f t="shared" si="3"/>
+        <v>31.158826714449638</v>
+      </c>
+    </row>
+    <row r="59" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B59" t="str">
+        <f>lc_detailed!AM59</f>
+        <v>SW_ESC</v>
+      </c>
+      <c r="C59" t="str">
+        <f>lc_detailed!AN59</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D59" s="21">
+        <f>lc_detailed!AU59/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="21">
+        <f>lc_detailed!AV59/$AM$3</f>
+        <v>-0.41182630936364006</v>
+      </c>
+      <c r="F59" s="21">
+        <f>lc_detailed!AW59/$AM$3</f>
+        <v>1.5877382663001753</v>
+      </c>
+      <c r="G59" s="21">
+        <f>lc_detailed!AX59/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H59" s="21">
+        <f>lc_detailed!AY59/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="21">
+        <f>lc_detailed!AZ59/$AM$3</f>
+        <v>6.2347194877488923E-2</v>
+      </c>
+      <c r="J59" s="21">
+        <f>lc_detailed!BA59/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K59" s="21">
+        <f>lc_detailed!BB59/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L59" s="21">
+        <f>lc_detailed!BC59/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M59" s="21">
+        <f>lc_detailed!BE59/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="21">
+        <f>lc_detailed!BF59/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O59" s="21">
+        <f>lc_detailed!BD59</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P59" s="21">
+        <f>lc_detailed!AO59</f>
+        <v>1040.3470427228478</v>
+      </c>
+      <c r="Q59" s="21">
+        <f t="shared" si="0"/>
+        <v>22.814628129887012</v>
+      </c>
+      <c r="R59" s="21">
+        <f t="shared" si="1"/>
+        <v>22.814628129887009</v>
+      </c>
+      <c r="T59" t="str">
+        <f>lc_detailed!AM59</f>
+        <v>SW_ESC</v>
+      </c>
+      <c r="U59" t="str">
+        <f>lc_detailed!AN59</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V59" s="21">
+        <f>lc_detailed!AU59/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W59" s="21">
+        <f>lc_detailed!AV59/$AM$3</f>
+        <v>-0.41182630936364006</v>
+      </c>
+      <c r="X59" s="21">
+        <f>lc_detailed!AW59/$AM$3</f>
+        <v>1.5877382663001753</v>
+      </c>
+      <c r="Y59" s="21">
+        <f>lc_detailed!AX59/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z59" s="21">
+        <f>lc_detailed!AY59/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA59" s="21">
+        <f>lc_detailed!AZ59/$AM$3</f>
+        <v>6.2347194877488923E-2</v>
+      </c>
+      <c r="AB59" s="21">
+        <f>lc_detailed!BA59/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC59" s="21">
+        <f>lc_detailed!BB59/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD59" s="21">
+        <f>lc_detailed!BC59/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE59" s="21">
+        <f>lc_detailed!BK59/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF59" s="21">
+        <f>lc_detailed!BL59/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG59" s="21">
+        <f>lc_detailed!BJ59</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH59" s="21">
+        <f>lc_detailed!AR59</f>
+        <v>1415.0322978116394</v>
+      </c>
+      <c r="AI59" s="21">
+        <f t="shared" si="2"/>
+        <v>31.031410039728932</v>
+      </c>
+      <c r="AJ59" s="21">
+        <f t="shared" si="3"/>
+        <v>31.031410039728929</v>
+      </c>
+    </row>
+    <row r="60" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B60" t="str">
+        <f>lc_detailed!AM60</f>
+        <v>NW_ESC</v>
+      </c>
+      <c r="C60" t="str">
+        <f>lc_detailed!AN60</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D60" s="21">
+        <f>lc_detailed!AU60/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="21">
+        <f>lc_detailed!AV60/$AM$3</f>
+        <v>-0.34583867569632065</v>
+      </c>
+      <c r="F60" s="21">
+        <f>lc_detailed!AW60/$AM$3</f>
+        <v>1.5075723568325916</v>
+      </c>
+      <c r="G60" s="21">
+        <f>lc_detailed!AX60/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H60" s="21">
+        <f>lc_detailed!AY60/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="21">
+        <f>lc_detailed!AZ60/$AM$3</f>
+        <v>0.11898449019851967</v>
+      </c>
+      <c r="J60" s="21">
+        <f>lc_detailed!BA60/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K60" s="21">
+        <f>lc_detailed!BB60/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L60" s="21">
+        <f>lc_detailed!BC60/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M60" s="21">
+        <f>lc_detailed!BE60/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N60" s="21">
+        <f>lc_detailed!BF60/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O60" s="21">
+        <f>lc_detailed!BD60</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P60" s="21">
+        <f>lc_detailed!AO60</f>
+        <v>1042.2831740129948</v>
+      </c>
+      <c r="Q60" s="21">
+        <f t="shared" si="0"/>
+        <v>22.857087149407779</v>
+      </c>
+      <c r="R60" s="21">
+        <f t="shared" si="1"/>
+        <v>22.857087149407775</v>
+      </c>
+      <c r="T60" t="str">
+        <f>lc_detailed!AM60</f>
+        <v>NW_ESC</v>
+      </c>
+      <c r="U60" t="str">
+        <f>lc_detailed!AN60</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V60" s="21">
+        <f>lc_detailed!AU60/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="21">
+        <f>lc_detailed!AV60/$AM$3</f>
+        <v>-0.34583867569632065</v>
+      </c>
+      <c r="X60" s="21">
+        <f>lc_detailed!AW60/$AM$3</f>
+        <v>1.5075723568325916</v>
+      </c>
+      <c r="Y60" s="21">
+        <f>lc_detailed!AX60/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z60" s="21">
+        <f>lc_detailed!AY60/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA60" s="21">
+        <f>lc_detailed!AZ60/$AM$3</f>
+        <v>0.11898449019851967</v>
+      </c>
+      <c r="AB60" s="21">
+        <f>lc_detailed!BA60/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC60" s="21">
+        <f>lc_detailed!BB60/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD60" s="21">
+        <f>lc_detailed!BC60/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE60" s="21">
+        <f>lc_detailed!BK60/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF60" s="21">
+        <f>lc_detailed!BL60/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG60" s="21">
+        <f>lc_detailed!BJ60</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH60" s="21">
+        <f>lc_detailed!AR60</f>
+        <v>1416.9684291017863</v>
+      </c>
+      <c r="AI60" s="21">
+        <f t="shared" si="2"/>
+        <v>31.073869059249699</v>
+      </c>
+      <c r="AJ60" s="21">
+        <f t="shared" si="3"/>
+        <v>31.073869059249695</v>
+      </c>
+    </row>
+    <row r="61" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B61" t="str">
+        <f>lc_detailed!AM61</f>
+        <v>TX_ESC</v>
+      </c>
+      <c r="C61" t="str">
+        <f>lc_detailed!AN61</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D61" s="21">
+        <f>lc_detailed!AU61/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="21">
+        <f>lc_detailed!AV61/$AM$3</f>
+        <v>-0.40004431463636292</v>
+      </c>
+      <c r="F61" s="21">
+        <f>lc_detailed!AW61/$AM$3</f>
+        <v>1.6564805480927998</v>
+      </c>
+      <c r="G61" s="21">
+        <f>lc_detailed!AX61/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H61" s="21">
+        <f>lc_detailed!AY61/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="21">
+        <f>lc_detailed!AZ61/$AM$3</f>
+        <v>7.2267236642152941E-2</v>
+      </c>
+      <c r="J61" s="21">
+        <f>lc_detailed!BA61/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K61" s="21">
+        <f>lc_detailed!BB61/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L61" s="21">
+        <f>lc_detailed!BC61/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M61" s="21">
+        <f>lc_detailed!BE61/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N61" s="21">
+        <f>lc_detailed!BF61/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O61" s="21">
+        <f>lc_detailed!BD61</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P61" s="21">
+        <f>lc_detailed!AO61</f>
+        <v>1044.471303636624</v>
+      </c>
+      <c r="Q61" s="21">
+        <f t="shared" si="0"/>
+        <v>22.90507244817158</v>
+      </c>
+      <c r="R61" s="21">
+        <f t="shared" si="1"/>
+        <v>22.905072448171573</v>
+      </c>
+      <c r="T61" t="str">
+        <f>lc_detailed!AM61</f>
+        <v>TX_ESC</v>
+      </c>
+      <c r="U61" t="str">
+        <f>lc_detailed!AN61</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V61" s="21">
+        <f>lc_detailed!AU61/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W61" s="21">
+        <f>lc_detailed!AV61/$AM$3</f>
+        <v>-0.40004431463636292</v>
+      </c>
+      <c r="X61" s="21">
+        <f>lc_detailed!AW61/$AM$3</f>
+        <v>1.6564805480927998</v>
+      </c>
+      <c r="Y61" s="21">
+        <f>lc_detailed!AX61/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z61" s="21">
+        <f>lc_detailed!AY61/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA61" s="21">
+        <f>lc_detailed!AZ61/$AM$3</f>
+        <v>7.2267236642152941E-2</v>
+      </c>
+      <c r="AB61" s="21">
+        <f>lc_detailed!BA61/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC61" s="21">
+        <f>lc_detailed!BB61/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD61" s="21">
+        <f>lc_detailed!BC61/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE61" s="21">
+        <f>lc_detailed!BK61/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF61" s="21">
+        <f>lc_detailed!BL61/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG61" s="21">
+        <f>lc_detailed!BJ61</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH61" s="21">
+        <f>lc_detailed!AR61</f>
+        <v>1419.1565587254156</v>
+      </c>
+      <c r="AI61" s="21">
+        <f t="shared" si="2"/>
+        <v>31.121854358013501</v>
+      </c>
+      <c r="AJ61" s="21">
+        <f t="shared" si="3"/>
+        <v>31.121854358013493</v>
+      </c>
+    </row>
+    <row r="62" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B62" t="str">
+        <f>lc_detailed!AM62</f>
+        <v>NCEN_ESC</v>
+      </c>
+      <c r="C62" t="str">
+        <f>lc_detailed!AN62</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D62" s="21">
+        <f>lc_detailed!AU62/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="21">
+        <f>lc_detailed!AV62/$AM$3</f>
+        <v>-0.44900706395587092</v>
+      </c>
+      <c r="F62" s="21">
+        <f>lc_detailed!AW62/$AM$3</f>
+        <v>1.7496268682811835</v>
+      </c>
+      <c r="G62" s="21">
+        <f>lc_detailed!AX62/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H62" s="21">
+        <f>lc_detailed!AY62/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="21">
+        <f>lc_detailed!AZ62/$AM$3</f>
+        <v>4.0240959893843069E-2</v>
+      </c>
+      <c r="J62" s="21">
+        <f>lc_detailed!BA62/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K62" s="21">
+        <f>lc_detailed!BB62/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L62" s="21">
+        <f>lc_detailed!BC62/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M62" s="21">
+        <f>lc_detailed!BE62/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N62" s="21">
+        <f>lc_detailed!BF62/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O62" s="21">
+        <f>lc_detailed!BD62</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P62" s="21">
+        <f>lc_detailed!AO62</f>
+        <v>1045.0256762485219</v>
+      </c>
+      <c r="Q62" s="21">
+        <f t="shared" si="0"/>
+        <v>22.917229742292147</v>
+      </c>
+      <c r="R62" s="21">
+        <f t="shared" si="1"/>
+        <v>22.917229742292143</v>
+      </c>
+      <c r="T62" t="str">
+        <f>lc_detailed!AM62</f>
+        <v>NCEN_ESC</v>
+      </c>
+      <c r="U62" t="str">
+        <f>lc_detailed!AN62</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V62" s="21">
+        <f>lc_detailed!AU62/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W62" s="21">
+        <f>lc_detailed!AV62/$AM$3</f>
+        <v>-0.44900706395587092</v>
+      </c>
+      <c r="X62" s="21">
+        <f>lc_detailed!AW62/$AM$3</f>
+        <v>1.7496268682811835</v>
+      </c>
+      <c r="Y62" s="21">
+        <f>lc_detailed!AX62/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z62" s="21">
+        <f>lc_detailed!AY62/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA62" s="21">
+        <f>lc_detailed!AZ62/$AM$3</f>
+        <v>4.0240959893843069E-2</v>
+      </c>
+      <c r="AB62" s="21">
+        <f>lc_detailed!BA62/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC62" s="21">
+        <f>lc_detailed!BB62/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD62" s="21">
+        <f>lc_detailed!BC62/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE62" s="21">
+        <f>lc_detailed!BK62/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF62" s="21">
+        <f>lc_detailed!BL62/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG62" s="21">
+        <f>lc_detailed!BJ62</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH62" s="21">
+        <f>lc_detailed!AR62</f>
+        <v>1419.7109313373135</v>
+      </c>
+      <c r="AI62" s="21">
+        <f t="shared" si="2"/>
+        <v>31.134011652134067</v>
+      </c>
+      <c r="AJ62" s="21">
+        <f t="shared" si="3"/>
+        <v>31.134011652134063</v>
+      </c>
+    </row>
+    <row r="63" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B63" t="str">
+        <f>lc_detailed!AM63</f>
+        <v>CEN_ESC</v>
+      </c>
+      <c r="C63" t="str">
+        <f>lc_detailed!AN63</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D63" s="21">
+        <f>lc_detailed!AU63/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="21">
+        <f>lc_detailed!AV63/$AM$3</f>
+        <v>-0.41514095054329514</v>
+      </c>
+      <c r="F63" s="21">
+        <f>lc_detailed!AW63/$AM$3</f>
+        <v>1.7017296877989159</v>
+      </c>
+      <c r="G63" s="21">
+        <f>lc_detailed!AX63/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H63" s="21">
+        <f>lc_detailed!AY63/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="21">
+        <f>lc_detailed!AZ63/$AM$3</f>
+        <v>6.9840858663496E-2</v>
+      </c>
+      <c r="J63" s="21">
+        <f>lc_detailed!BA63/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K63" s="21">
+        <f>lc_detailed!BB63/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L63" s="21">
+        <f>lc_detailed!BC63/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M63" s="21">
+        <f>lc_detailed!BE63/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N63" s="21">
+        <f>lc_detailed!BF63/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O63" s="21">
+        <f>lc_detailed!BD63</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P63" s="21">
+        <f>lc_detailed!AO63</f>
+        <v>1045.7356149740401</v>
+      </c>
+      <c r="Q63" s="21">
+        <f t="shared" si="0"/>
+        <v>22.932798573992105</v>
+      </c>
+      <c r="R63" s="21">
+        <f t="shared" si="1"/>
+        <v>22.932798573992102</v>
+      </c>
+      <c r="T63" t="str">
+        <f>lc_detailed!AM63</f>
+        <v>CEN_ESC</v>
+      </c>
+      <c r="U63" t="str">
+        <f>lc_detailed!AN63</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V63" s="21">
+        <f>lc_detailed!AU63/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W63" s="21">
+        <f>lc_detailed!AV63/$AM$3</f>
+        <v>-0.41514095054329514</v>
+      </c>
+      <c r="X63" s="21">
+        <f>lc_detailed!AW63/$AM$3</f>
+        <v>1.7017296877989159</v>
+      </c>
+      <c r="Y63" s="21">
+        <f>lc_detailed!AX63/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z63" s="21">
+        <f>lc_detailed!AY63/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA63" s="21">
+        <f>lc_detailed!AZ63/$AM$3</f>
+        <v>6.9840858663496E-2</v>
+      </c>
+      <c r="AB63" s="21">
+        <f>lc_detailed!BA63/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC63" s="21">
+        <f>lc_detailed!BB63/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD63" s="21">
+        <f>lc_detailed!BC63/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE63" s="21">
+        <f>lc_detailed!BK63/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF63" s="21">
+        <f>lc_detailed!BL63/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG63" s="21">
+        <f>lc_detailed!BJ63</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH63" s="21">
+        <f>lc_detailed!AR63</f>
+        <v>1420.4208700628317</v>
+      </c>
+      <c r="AI63" s="21">
+        <f t="shared" si="2"/>
+        <v>31.149580483834026</v>
+      </c>
+      <c r="AJ63" s="21">
+        <f t="shared" si="3"/>
+        <v>31.149580483834022</v>
+      </c>
+    </row>
+    <row r="64" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B64" t="str">
+        <f>lc_detailed!AM64</f>
+        <v>SE_ESC</v>
+      </c>
+      <c r="C64" t="str">
+        <f>lc_detailed!AN64</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D64" s="21">
+        <f>lc_detailed!AU64/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="21">
+        <f>lc_detailed!AV64/$AM$3</f>
+        <v>-0.41197926741210172</v>
+      </c>
+      <c r="F64" s="21">
+        <f>lc_detailed!AW64/$AM$3</f>
+        <v>1.6683935701232369</v>
+      </c>
+      <c r="G64" s="21">
+        <f>lc_detailed!AX64/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H64" s="21">
+        <f>lc_detailed!AY64/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="21">
+        <f>lc_detailed!AZ64/$AM$3</f>
+        <v>7.0859936438730925E-2</v>
+      </c>
+      <c r="J64" s="21">
+        <f>lc_detailed!BA64/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K64" s="21">
+        <f>lc_detailed!BB64/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L64" s="21">
+        <f>lc_detailed!BC64/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M64" s="21">
+        <f>lc_detailed!BE64/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="21">
+        <f>lc_detailed!BF64/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O64" s="21">
+        <f>lc_detailed!BD64</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P64" s="21">
+        <f>lc_detailed!AO64</f>
+        <v>1044.4061307053623</v>
+      </c>
+      <c r="Q64" s="21">
+        <f t="shared" si="0"/>
+        <v>22.903643217222857</v>
+      </c>
+      <c r="R64" s="21">
+        <f t="shared" si="1"/>
+        <v>22.90364321722285</v>
+      </c>
+      <c r="T64" t="str">
+        <f>lc_detailed!AM64</f>
+        <v>SE_ESC</v>
+      </c>
+      <c r="U64" t="str">
+        <f>lc_detailed!AN64</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V64" s="21">
+        <f>lc_detailed!AU64/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W64" s="21">
+        <f>lc_detailed!AV64/$AM$3</f>
+        <v>-0.41197926741210172</v>
+      </c>
+      <c r="X64" s="21">
+        <f>lc_detailed!AW64/$AM$3</f>
+        <v>1.6683935701232369</v>
+      </c>
+      <c r="Y64" s="21">
+        <f>lc_detailed!AX64/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z64" s="21">
+        <f>lc_detailed!AY64/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA64" s="21">
+        <f>lc_detailed!AZ64/$AM$3</f>
+        <v>7.0859936438730925E-2</v>
+      </c>
+      <c r="AB64" s="21">
+        <f>lc_detailed!BA64/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC64" s="21">
+        <f>lc_detailed!BB64/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD64" s="21">
+        <f>lc_detailed!BC64/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE64" s="21">
+        <f>lc_detailed!BK64/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF64" s="21">
+        <f>lc_detailed!BL64/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG64" s="21">
+        <f>lc_detailed!BJ64</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH64" s="21">
+        <f>lc_detailed!AR64</f>
+        <v>1419.0913857941539</v>
+      </c>
+      <c r="AI64" s="21">
+        <f t="shared" si="2"/>
+        <v>31.120425127064777</v>
+      </c>
+      <c r="AJ64" s="21">
+        <f t="shared" si="3"/>
+        <v>31.12042512706477</v>
+      </c>
+    </row>
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B65" t="str">
+        <f>lc_detailed!AM65</f>
+        <v>MIDAT_ESC</v>
+      </c>
+      <c r="C65" t="str">
+        <f>lc_detailed!AN65</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D65" s="21">
+        <f>lc_detailed!AU65/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="21">
+        <f>lc_detailed!AV65/$AM$3</f>
+        <v>-0.5311353695838219</v>
+      </c>
+      <c r="F65" s="21">
+        <f>lc_detailed!AW65/$AM$3</f>
+        <v>1.7150892368794102</v>
+      </c>
+      <c r="G65" s="21">
+        <f>lc_detailed!AX65/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H65" s="21">
+        <f>lc_detailed!AY65/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="21">
+        <f>lc_detailed!AZ65/$AM$3</f>
+        <v>4.5385577930510373E-2</v>
+      </c>
+      <c r="J65" s="21">
+        <f>lc_detailed!BA65/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K65" s="21">
+        <f>lc_detailed!BB65/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L65" s="21">
+        <f>lc_detailed!BC65/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M65" s="21">
+        <f>lc_detailed!BE65/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N65" s="21">
+        <f>lc_detailed!BF65/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O65" s="21">
+        <f>lc_detailed!BD65</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P65" s="21">
+        <f>lc_detailed!AO65</f>
+        <v>1039.9403041024384</v>
+      </c>
+      <c r="Q65" s="21">
+        <f t="shared" si="0"/>
+        <v>22.805708423299087</v>
+      </c>
+      <c r="R65" s="21">
+        <f t="shared" si="1"/>
+        <v>22.805708423299084</v>
+      </c>
+      <c r="T65" t="str">
+        <f>lc_detailed!AM65</f>
+        <v>MIDAT_ESC</v>
+      </c>
+      <c r="U65" t="str">
+        <f>lc_detailed!AN65</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V65" s="21">
+        <f>lc_detailed!AU65/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W65" s="21">
+        <f>lc_detailed!AV65/$AM$3</f>
+        <v>-0.5311353695838219</v>
+      </c>
+      <c r="X65" s="21">
+        <f>lc_detailed!AW65/$AM$3</f>
+        <v>1.7150892368794102</v>
+      </c>
+      <c r="Y65" s="21">
+        <f>lc_detailed!AX65/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z65" s="21">
+        <f>lc_detailed!AY65/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA65" s="21">
+        <f>lc_detailed!AZ65/$AM$3</f>
+        <v>4.5385577930510373E-2</v>
+      </c>
+      <c r="AB65" s="21">
+        <f>lc_detailed!BA65/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC65" s="21">
+        <f>lc_detailed!BB65/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD65" s="21">
+        <f>lc_detailed!BC65/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE65" s="21">
+        <f>lc_detailed!BK65/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF65" s="21">
+        <f>lc_detailed!BL65/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG65" s="21">
+        <f>lc_detailed!BJ65</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH65" s="21">
+        <f>lc_detailed!AR65</f>
+        <v>1414.62555919123</v>
+      </c>
+      <c r="AI65" s="21">
+        <f t="shared" si="2"/>
+        <v>31.022490333141008</v>
+      </c>
+      <c r="AJ65" s="21">
+        <f t="shared" si="3"/>
+        <v>31.022490333141004</v>
+      </c>
+    </row>
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B66" t="str">
+        <f>lc_detailed!AM66</f>
+        <v>NE_ESC</v>
+      </c>
+      <c r="C66" t="str">
+        <f>lc_detailed!AN66</f>
+        <v>Ethane</v>
+      </c>
+      <c r="D66" s="21">
+        <f>lc_detailed!AU66/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="21">
+        <f>lc_detailed!AV66/$AM$3</f>
+        <v>-0.82828077146940482</v>
+      </c>
+      <c r="F66" s="21">
+        <f>lc_detailed!AW66/$AM$3</f>
+        <v>1.6580314033969319</v>
+      </c>
+      <c r="G66" s="21">
+        <f>lc_detailed!AX66/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="H66" s="21">
+        <f>lc_detailed!AY66/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="21">
+        <f>lc_detailed!AZ66/$AM$3</f>
+        <v>-0.28731138259593558</v>
+      </c>
+      <c r="J66" s="21">
+        <f>lc_detailed!BA66/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="K66" s="21">
+        <f>lc_detailed!BB66/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="L66" s="21">
+        <f>lc_detailed!BC66/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="M66" s="21">
+        <f>lc_detailed!BE66/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="N66" s="21">
+        <f>lc_detailed!BF66/$AM$3</f>
+        <v>0.93554445913605078</v>
+      </c>
+      <c r="O66" s="21">
+        <f>lc_detailed!BD66</f>
+        <v>0.42697847224104163</v>
+      </c>
+      <c r="P66" s="21">
+        <f>lc_detailed!AO66</f>
+        <v>1008.617655169649</v>
+      </c>
+      <c r="Q66" s="21">
+        <f t="shared" si="0"/>
+        <v>22.118808227404582</v>
+      </c>
+      <c r="R66" s="21">
+        <f t="shared" si="1"/>
+        <v>22.118808227404578</v>
+      </c>
+      <c r="T66" t="str">
+        <f>lc_detailed!AM66</f>
+        <v>NE_ESC</v>
+      </c>
+      <c r="U66" t="str">
+        <f>lc_detailed!AN66</f>
+        <v>Ethane</v>
+      </c>
+      <c r="V66" s="21">
+        <f>lc_detailed!AU66/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="W66" s="21">
+        <f>lc_detailed!AV66/$AM$3</f>
+        <v>-0.82828077146940482</v>
+      </c>
+      <c r="X66" s="21">
+        <f>lc_detailed!AW66/$AM$3</f>
+        <v>1.6580314033969319</v>
+      </c>
+      <c r="Y66" s="21">
+        <f>lc_detailed!AX66/$AM$3</f>
+        <v>9.079842636033753</v>
+      </c>
+      <c r="Z66" s="21">
+        <f>lc_detailed!AY66/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AA66" s="21">
+        <f>lc_detailed!AZ66/$AM$3</f>
+        <v>-0.28731138259593558</v>
+      </c>
+      <c r="AB66" s="21">
+        <f>lc_detailed!BA66/$AM$3</f>
+        <v>6.8789631956535189</v>
+      </c>
+      <c r="AC66" s="21">
+        <f>lc_detailed!BB66/$AM$3</f>
+        <v>3.7649438231017713</v>
+      </c>
+      <c r="AD66" s="21">
+        <f>lc_detailed!BC66/$AM$3</f>
+        <v>0.91707486414789374</v>
+      </c>
+      <c r="AE66" s="21">
+        <f>lc_detailed!BK66/$AM$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF66" s="21">
+        <f>lc_detailed!BL66/$AM$3</f>
+        <v>9.1523263689779704</v>
+      </c>
+      <c r="AG66" s="21">
+        <f>lc_detailed!BJ66</f>
+        <v>4.1770824382695828</v>
+      </c>
+      <c r="AH66" s="21">
+        <f>lc_detailed!AR66</f>
+        <v>1383.3029102584405</v>
+      </c>
+      <c r="AI66" s="21">
+        <f t="shared" si="2"/>
+        <v>30.335590137246502</v>
+      </c>
+      <c r="AJ66" s="21">
+        <f t="shared" si="3"/>
+        <v>30.335590137246498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>